--- a/marketing/daily-ideas/pipeline/BuildCopilot-daily-ideas-pipeline-2026-27.xlsx
+++ b/marketing/daily-ideas/pipeline/BuildCopilot-daily-ideas-pipeline-2026-27.xlsx
@@ -755,8 +755,16 @@
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -819,8 +827,16 @@
       <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="2" t="inlineStr"/>
       <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -891,8 +907,16 @@
           <t>Trial one reporting task properly</t>
         </is>
       </c>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -967,8 +991,16 @@
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -1027,8 +1059,16 @@
       <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="2" t="inlineStr"/>
       <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -1095,8 +1135,16 @@
       </c>
       <c r="O7" s="2" t="inlineStr"/>
       <c r="P7" s="2" t="inlineStr"/>
-      <c r="Q7" s="2" t="inlineStr"/>
-      <c r="R7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -1159,8 +1207,16 @@
       </c>
       <c r="O8" s="2" t="inlineStr"/>
       <c r="P8" s="2" t="inlineStr"/>
-      <c r="Q8" s="2" t="inlineStr"/>
-      <c r="R8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -1227,8 +1283,16 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr"/>
-      <c r="R9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -1291,8 +1355,16 @@
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr"/>
       <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="2" t="inlineStr"/>
-      <c r="R10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -1359,8 +1431,16 @@
           <t>Invoice with no project reference: what should the workflow do?</t>
         </is>
       </c>
-      <c r="Q11" s="2" t="inlineStr"/>
-      <c r="R11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1431,8 +1511,16 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr"/>
-      <c r="Q12" s="2" t="inlineStr"/>
-      <c r="R12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -1491,8 +1579,16 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr"/>
       <c r="P13" s="2" t="inlineStr"/>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1559,8 +1655,16 @@
       </c>
       <c r="O14" s="2" t="inlineStr"/>
       <c r="P14" s="2" t="inlineStr"/>
-      <c r="Q14" s="2" t="inlineStr"/>
-      <c r="R14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1619,8 +1723,16 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr"/>
       <c r="P15" s="2" t="inlineStr"/>
-      <c r="Q15" s="2" t="inlineStr"/>
-      <c r="R15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1695,8 +1807,16 @@
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr"/>
-      <c r="Q16" s="2" t="inlineStr"/>
-      <c r="R16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1759,8 +1879,16 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr"/>
       <c r="P17" s="2" t="inlineStr"/>
-      <c r="Q17" s="2" t="inlineStr"/>
-      <c r="R17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1831,8 +1959,16 @@
           <t>Meeting actions need an owner and a date</t>
         </is>
       </c>
-      <c r="Q18" s="2" t="inlineStr"/>
-      <c r="R18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1903,8 +2039,16 @@
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr"/>
-      <c r="Q19" s="2" t="inlineStr"/>
-      <c r="R19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1963,8 +2107,16 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr"/>
       <c r="P20" s="2" t="inlineStr"/>
-      <c r="Q20" s="2" t="inlineStr"/>
-      <c r="R20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -2031,8 +2183,16 @@
       </c>
       <c r="O21" s="2" t="inlineStr"/>
       <c r="P21" s="2" t="inlineStr"/>
-      <c r="Q21" s="2" t="inlineStr"/>
-      <c r="R21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -2091,8 +2251,16 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr"/>
       <c r="P22" s="2" t="inlineStr"/>
-      <c r="Q22" s="2" t="inlineStr"/>
-      <c r="R22" s="2" t="inlineStr"/>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -2163,8 +2331,16 @@
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr"/>
-      <c r="Q23" s="2" t="inlineStr"/>
-      <c r="R23" s="2" t="inlineStr"/>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -2223,8 +2399,16 @@
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr"/>
       <c r="P24" s="2" t="inlineStr"/>
-      <c r="Q24" s="2" t="inlineStr"/>
-      <c r="R24" s="2" t="inlineStr"/>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -2287,8 +2471,16 @@
           <t>Don't make a chat response the cash-flow model</t>
         </is>
       </c>
-      <c r="Q25" s="2" t="inlineStr"/>
-      <c r="R25" s="2" t="inlineStr"/>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -2359,8 +2551,16 @@
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr"/>
-      <c r="Q26" s="2" t="inlineStr"/>
-      <c r="R26" s="2" t="inlineStr"/>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -2423,8 +2623,16 @@
       </c>
       <c r="O27" s="2" t="inlineStr"/>
       <c r="P27" s="2" t="inlineStr"/>
-      <c r="Q27" s="2" t="inlineStr"/>
-      <c r="R27" s="2" t="inlineStr"/>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -2483,8 +2691,16 @@
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr"/>
       <c r="P28" s="2" t="inlineStr"/>
-      <c r="Q28" s="2" t="inlineStr"/>
-      <c r="R28" s="2" t="inlineStr"/>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -2547,8 +2763,16 @@
       </c>
       <c r="O29" s="2" t="inlineStr"/>
       <c r="P29" s="2" t="inlineStr"/>
-      <c r="Q29" s="2" t="inlineStr"/>
-      <c r="R29" s="2" t="inlineStr"/>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -2619,8 +2843,16 @@
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr"/>
-      <c r="Q30" s="2" t="inlineStr"/>
-      <c r="R30" s="2" t="inlineStr"/>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -2679,8 +2911,16 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr"/>
       <c r="P31" s="2" t="inlineStr"/>
-      <c r="Q31" s="2" t="inlineStr"/>
-      <c r="R31" s="2" t="inlineStr"/>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -2747,8 +2987,16 @@
           <t>Friday updates from four places</t>
         </is>
       </c>
-      <c r="Q32" s="2" t="inlineStr"/>
-      <c r="R32" s="2" t="inlineStr"/>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -2815,8 +3063,16 @@
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr"/>
-      <c r="Q33" s="2" t="inlineStr"/>
-      <c r="R33" s="2" t="inlineStr"/>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -2879,8 +3135,16 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr"/>
       <c r="P34" s="2" t="inlineStr"/>
-      <c r="Q34" s="2" t="inlineStr"/>
-      <c r="R34" s="2" t="inlineStr"/>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -2943,8 +3207,16 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr"/>
       <c r="P35" s="2" t="inlineStr"/>
-      <c r="Q35" s="2" t="inlineStr"/>
-      <c r="R35" s="2" t="inlineStr"/>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -3003,8 +3275,16 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr"/>
       <c r="P36" s="2" t="inlineStr"/>
-      <c r="Q36" s="2" t="inlineStr"/>
-      <c r="R36" s="2" t="inlineStr"/>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -3075,8 +3355,16 @@
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr"/>
-      <c r="Q37" s="2" t="inlineStr"/>
-      <c r="R37" s="2" t="inlineStr"/>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -3139,8 +3427,16 @@
       </c>
       <c r="O38" s="2" t="inlineStr"/>
       <c r="P38" s="2" t="inlineStr"/>
-      <c r="Q38" s="2" t="inlineStr"/>
-      <c r="R38" s="2" t="inlineStr"/>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -3207,8 +3503,16 @@
           <t>Who owns the outstanding records at closeout?</t>
         </is>
       </c>
-      <c r="Q39" s="2" t="inlineStr"/>
-      <c r="R39" s="2" t="inlineStr"/>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -3283,8 +3587,16 @@
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr"/>
-      <c r="Q40" s="2" t="inlineStr"/>
-      <c r="R40" s="2" t="inlineStr"/>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -3351,8 +3663,16 @@
       </c>
       <c r="O41" s="2" t="inlineStr"/>
       <c r="P41" s="2" t="inlineStr"/>
-      <c r="Q41" s="2" t="inlineStr"/>
-      <c r="R41" s="2" t="inlineStr"/>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -3419,8 +3739,16 @@
       </c>
       <c r="O42" s="2" t="inlineStr"/>
       <c r="P42" s="2" t="inlineStr"/>
-      <c r="Q42" s="2" t="inlineStr"/>
-      <c r="R42" s="2" t="inlineStr"/>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -3483,8 +3811,16 @@
       </c>
       <c r="O43" s="2" t="inlineStr"/>
       <c r="P43" s="2" t="inlineStr"/>
-      <c r="Q43" s="2" t="inlineStr"/>
-      <c r="R43" s="2" t="inlineStr"/>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -3555,8 +3891,16 @@
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr"/>
-      <c r="Q44" s="2" t="inlineStr"/>
-      <c r="R44" s="2" t="inlineStr"/>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
@@ -3615,8 +3959,16 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr"/>
       <c r="P45" s="2" t="inlineStr"/>
-      <c r="Q45" s="2" t="inlineStr"/>
-      <c r="R45" s="2" t="inlineStr"/>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -3679,8 +4031,16 @@
           <t>Bring me one recurring task</t>
         </is>
       </c>
-      <c r="Q46" s="2" t="inlineStr"/>
-      <c r="R46" s="2" t="inlineStr"/>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -3751,8 +4111,16 @@
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr"/>
-      <c r="Q47" s="2" t="inlineStr"/>
-      <c r="R47" s="2" t="inlineStr"/>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -3811,8 +4179,16 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr"/>
       <c r="P48" s="2" t="inlineStr"/>
-      <c r="Q48" s="2" t="inlineStr"/>
-      <c r="R48" s="2" t="inlineStr"/>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
@@ -3879,8 +4255,16 @@
       </c>
       <c r="O49" s="2" t="inlineStr"/>
       <c r="P49" s="2" t="inlineStr"/>
-      <c r="Q49" s="2" t="inlineStr"/>
-      <c r="R49" s="2" t="inlineStr"/>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -3943,8 +4327,16 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr"/>
       <c r="P50" s="2" t="inlineStr"/>
-      <c r="Q50" s="2" t="inlineStr"/>
-      <c r="R50" s="2" t="inlineStr"/>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -4015,8 +4407,16 @@
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr"/>
-      <c r="Q51" s="2" t="inlineStr"/>
-      <c r="R51" s="2" t="inlineStr"/>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -4079,8 +4479,16 @@
       </c>
       <c r="O52" s="2" t="inlineStr"/>
       <c r="P52" s="2" t="inlineStr"/>
-      <c r="Q52" s="2" t="inlineStr"/>
-      <c r="R52" s="2" t="inlineStr"/>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -4139,8 +4547,16 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr"/>
       <c r="P53" s="2" t="inlineStr"/>
-      <c r="Q53" s="2" t="inlineStr"/>
-      <c r="R53" s="2" t="inlineStr"/>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -4207,8 +4623,16 @@
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr"/>
-      <c r="Q54" s="2" t="inlineStr"/>
-      <c r="R54" s="2" t="inlineStr"/>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -4267,8 +4691,16 @@
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr"/>
       <c r="P55" s="2" t="inlineStr"/>
-      <c r="Q55" s="2" t="inlineStr"/>
-      <c r="R55" s="2" t="inlineStr"/>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -4335,8 +4767,16 @@
       </c>
       <c r="O56" s="2" t="inlineStr"/>
       <c r="P56" s="2" t="inlineStr"/>
-      <c r="Q56" s="2" t="inlineStr"/>
-      <c r="R56" s="2" t="inlineStr"/>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
@@ -4399,8 +4839,16 @@
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr"/>
       <c r="P57" s="2" t="inlineStr"/>
-      <c r="Q57" s="2" t="inlineStr"/>
-      <c r="R57" s="2" t="inlineStr"/>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -4471,8 +4919,16 @@
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr"/>
-      <c r="Q58" s="2" t="inlineStr"/>
-      <c r="R58" s="2" t="inlineStr"/>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
@@ -4535,8 +4991,16 @@
       </c>
       <c r="O59" s="2" t="inlineStr"/>
       <c r="P59" s="2" t="inlineStr"/>
-      <c r="Q59" s="2" t="inlineStr"/>
-      <c r="R59" s="2" t="inlineStr"/>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -4595,8 +5059,16 @@
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr"/>
       <c r="P60" s="2" t="inlineStr"/>
-      <c r="Q60" s="2" t="inlineStr"/>
-      <c r="R60" s="2" t="inlineStr"/>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
@@ -4663,8 +5135,16 @@
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr"/>
-      <c r="Q61" s="2" t="inlineStr"/>
-      <c r="R61" s="2" t="inlineStr"/>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
@@ -4727,8 +5207,16 @@
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr"/>
       <c r="P62" s="2" t="inlineStr"/>
-      <c r="Q62" s="2" t="inlineStr"/>
-      <c r="R62" s="2" t="inlineStr"/>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
@@ -4787,8 +5275,16 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr"/>
       <c r="P63" s="2" t="inlineStr"/>
-      <c r="Q63" s="2" t="inlineStr"/>
-      <c r="R63" s="2" t="inlineStr"/>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -4851,8 +5347,16 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr"/>
       <c r="P64" s="2" t="inlineStr"/>
-      <c r="Q64" s="2" t="inlineStr"/>
-      <c r="R64" s="2" t="inlineStr"/>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
@@ -4919,8 +5423,16 @@
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr"/>
-      <c r="Q65" s="2" t="inlineStr"/>
-      <c r="R65" s="2" t="inlineStr"/>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -4983,8 +5495,16 @@
       </c>
       <c r="O66" s="2" t="inlineStr"/>
       <c r="P66" s="2" t="inlineStr"/>
-      <c r="Q66" s="2" t="inlineStr"/>
-      <c r="R66" s="2" t="inlineStr"/>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
@@ -5043,8 +5563,16 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr"/>
       <c r="P67" s="2" t="inlineStr"/>
-      <c r="Q67" s="2" t="inlineStr"/>
-      <c r="R67" s="2" t="inlineStr"/>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
@@ -5107,8 +5635,16 @@
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr"/>
-      <c r="Q68" s="2" t="inlineStr"/>
-      <c r="R68" s="2" t="inlineStr"/>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
@@ -5171,8 +5707,16 @@
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr"/>
       <c r="P69" s="2" t="inlineStr"/>
-      <c r="Q69" s="2" t="inlineStr"/>
-      <c r="R69" s="2" t="inlineStr"/>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
@@ -5239,8 +5783,16 @@
       </c>
       <c r="O70" s="2" t="inlineStr"/>
       <c r="P70" s="2" t="inlineStr"/>
-      <c r="Q70" s="2" t="inlineStr"/>
-      <c r="R70" s="2" t="inlineStr"/>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
@@ -5299,8 +5851,16 @@
       <c r="N71" s="2" t="inlineStr"/>
       <c r="O71" s="2" t="inlineStr"/>
       <c r="P71" s="2" t="inlineStr"/>
-      <c r="Q71" s="2" t="inlineStr"/>
-      <c r="R71" s="2" t="inlineStr"/>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
@@ -5363,8 +5923,16 @@
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr"/>
-      <c r="Q72" s="2" t="inlineStr"/>
-      <c r="R72" s="2" t="inlineStr"/>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
@@ -5427,8 +5995,16 @@
       </c>
       <c r="O73" s="2" t="inlineStr"/>
       <c r="P73" s="2" t="inlineStr"/>
-      <c r="Q73" s="2" t="inlineStr"/>
-      <c r="R73" s="2" t="inlineStr"/>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
@@ -5491,8 +6067,16 @@
       </c>
       <c r="O74" s="2" t="inlineStr"/>
       <c r="P74" s="2" t="inlineStr"/>
-      <c r="Q74" s="2" t="inlineStr"/>
-      <c r="R74" s="2" t="inlineStr"/>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
@@ -5567,8 +6151,16 @@
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr"/>
-      <c r="Q75" s="2" t="inlineStr"/>
-      <c r="R75" s="2" t="inlineStr"/>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
@@ -5627,8 +6219,16 @@
       <c r="N76" s="2" t="inlineStr"/>
       <c r="O76" s="2" t="inlineStr"/>
       <c r="P76" s="2" t="inlineStr"/>
-      <c r="Q76" s="2" t="inlineStr"/>
-      <c r="R76" s="2" t="inlineStr"/>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
@@ -5695,8 +6295,16 @@
       </c>
       <c r="O77" s="2" t="inlineStr"/>
       <c r="P77" s="2" t="inlineStr"/>
-      <c r="Q77" s="2" t="inlineStr"/>
-      <c r="R77" s="2" t="inlineStr"/>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
@@ -5755,8 +6363,16 @@
       <c r="N78" s="2" t="inlineStr"/>
       <c r="O78" s="2" t="inlineStr"/>
       <c r="P78" s="2" t="inlineStr"/>
-      <c r="Q78" s="2" t="inlineStr"/>
-      <c r="R78" s="2" t="inlineStr"/>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
@@ -5819,8 +6435,16 @@
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr"/>
-      <c r="Q79" s="2" t="inlineStr"/>
-      <c r="R79" s="2" t="inlineStr"/>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
@@ -5879,8 +6503,16 @@
       <c r="N80" s="2" t="inlineStr"/>
       <c r="O80" s="2" t="inlineStr"/>
       <c r="P80" s="2" t="inlineStr"/>
-      <c r="Q80" s="2" t="inlineStr"/>
-      <c r="R80" s="2" t="inlineStr"/>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
@@ -5939,8 +6571,16 @@
       <c r="N81" s="2" t="inlineStr"/>
       <c r="O81" s="2" t="inlineStr"/>
       <c r="P81" s="2" t="inlineStr"/>
-      <c r="Q81" s="2" t="inlineStr"/>
-      <c r="R81" s="2" t="inlineStr"/>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
@@ -6007,8 +6647,16 @@
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr"/>
-      <c r="Q82" s="2" t="inlineStr"/>
-      <c r="R82" s="2" t="inlineStr"/>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
@@ -6067,8 +6715,16 @@
       <c r="N83" s="2" t="inlineStr"/>
       <c r="O83" s="2" t="inlineStr"/>
       <c r="P83" s="2" t="inlineStr"/>
-      <c r="Q83" s="2" t="inlineStr"/>
-      <c r="R83" s="2" t="inlineStr"/>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
@@ -6135,8 +6791,16 @@
       </c>
       <c r="O84" s="2" t="inlineStr"/>
       <c r="P84" s="2" t="inlineStr"/>
-      <c r="Q84" s="2" t="inlineStr"/>
-      <c r="R84" s="2" t="inlineStr"/>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
@@ -6195,8 +6859,16 @@
       <c r="N85" s="2" t="inlineStr"/>
       <c r="O85" s="2" t="inlineStr"/>
       <c r="P85" s="2" t="inlineStr"/>
-      <c r="Q85" s="2" t="inlineStr"/>
-      <c r="R85" s="2" t="inlineStr"/>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
@@ -6259,8 +6931,16 @@
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr"/>
-      <c r="Q86" s="2" t="inlineStr"/>
-      <c r="R86" s="2" t="inlineStr"/>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
@@ -6323,8 +7003,16 @@
       <c r="N87" s="2" t="inlineStr"/>
       <c r="O87" s="2" t="inlineStr"/>
       <c r="P87" s="2" t="inlineStr"/>
-      <c r="Q87" s="2" t="inlineStr"/>
-      <c r="R87" s="2" t="inlineStr"/>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
@@ -6383,8 +7071,16 @@
       <c r="N88" s="2" t="inlineStr"/>
       <c r="O88" s="2" t="inlineStr"/>
       <c r="P88" s="2" t="inlineStr"/>
-      <c r="Q88" s="2" t="inlineStr"/>
-      <c r="R88" s="2" t="inlineStr"/>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
@@ -6455,8 +7151,16 @@
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr"/>
-      <c r="Q89" s="2" t="inlineStr"/>
-      <c r="R89" s="2" t="inlineStr"/>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
@@ -6515,8 +7219,16 @@
       <c r="N90" s="2" t="inlineStr"/>
       <c r="O90" s="2" t="inlineStr"/>
       <c r="P90" s="2" t="inlineStr"/>
-      <c r="Q90" s="2" t="inlineStr"/>
-      <c r="R90" s="2" t="inlineStr"/>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
@@ -6579,8 +7291,16 @@
       </c>
       <c r="O91" s="2" t="inlineStr"/>
       <c r="P91" s="2" t="inlineStr"/>
-      <c r="Q91" s="2" t="inlineStr"/>
-      <c r="R91" s="2" t="inlineStr"/>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
@@ -6643,8 +7363,16 @@
       <c r="N92" s="2" t="inlineStr"/>
       <c r="O92" s="2" t="inlineStr"/>
       <c r="P92" s="2" t="inlineStr"/>
-      <c r="Q92" s="2" t="inlineStr"/>
-      <c r="R92" s="2" t="inlineStr"/>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
@@ -6711,8 +7439,16 @@
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr"/>
-      <c r="Q93" s="2" t="inlineStr"/>
-      <c r="R93" s="2" t="inlineStr"/>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
@@ -6775,8 +7511,16 @@
       <c r="N94" s="2" t="inlineStr"/>
       <c r="O94" s="2" t="inlineStr"/>
       <c r="P94" s="2" t="inlineStr"/>
-      <c r="Q94" s="2" t="inlineStr"/>
-      <c r="R94" s="2" t="inlineStr"/>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
@@ -6835,8 +7579,16 @@
       <c r="N95" s="2" t="inlineStr"/>
       <c r="O95" s="2" t="inlineStr"/>
       <c r="P95" s="2" t="inlineStr"/>
-      <c r="Q95" s="2" t="inlineStr"/>
-      <c r="R95" s="2" t="inlineStr"/>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
@@ -6907,8 +7659,16 @@
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr"/>
-      <c r="Q96" s="2" t="inlineStr"/>
-      <c r="R96" s="2" t="inlineStr"/>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
@@ -6967,8 +7727,16 @@
       <c r="N97" s="2" t="inlineStr"/>
       <c r="O97" s="2" t="inlineStr"/>
       <c r="P97" s="2" t="inlineStr"/>
-      <c r="Q97" s="2" t="inlineStr"/>
-      <c r="R97" s="2" t="inlineStr"/>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
@@ -7035,8 +7803,16 @@
       </c>
       <c r="O98" s="2" t="inlineStr"/>
       <c r="P98" s="2" t="inlineStr"/>
-      <c r="Q98" s="2" t="inlineStr"/>
-      <c r="R98" s="2" t="inlineStr"/>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
@@ -7099,8 +7875,16 @@
       <c r="N99" s="2" t="inlineStr"/>
       <c r="O99" s="2" t="inlineStr"/>
       <c r="P99" s="2" t="inlineStr"/>
-      <c r="Q99" s="2" t="inlineStr"/>
-      <c r="R99" s="2" t="inlineStr"/>
+      <c r="Q99" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R99" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
@@ -7163,8 +7947,16 @@
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr"/>
-      <c r="Q100" s="2" t="inlineStr"/>
-      <c r="R100" s="2" t="inlineStr"/>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
@@ -7227,8 +8019,16 @@
       </c>
       <c r="O101" s="2" t="inlineStr"/>
       <c r="P101" s="2" t="inlineStr"/>
-      <c r="Q101" s="2" t="inlineStr"/>
-      <c r="R101" s="2" t="inlineStr"/>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R101" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
@@ -7287,8 +8087,16 @@
       <c r="N102" s="2" t="inlineStr"/>
       <c r="O102" s="2" t="inlineStr"/>
       <c r="P102" s="2" t="inlineStr"/>
-      <c r="Q102" s="2" t="inlineStr"/>
-      <c r="R102" s="2" t="inlineStr"/>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R102" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
@@ -7355,8 +8163,16 @@
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr"/>
-      <c r="Q103" s="2" t="inlineStr"/>
-      <c r="R103" s="2" t="inlineStr"/>
+      <c r="Q103" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R103" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
@@ -7419,8 +8235,16 @@
       <c r="N104" s="2" t="inlineStr"/>
       <c r="O104" s="2" t="inlineStr"/>
       <c r="P104" s="2" t="inlineStr"/>
-      <c r="Q104" s="2" t="inlineStr"/>
-      <c r="R104" s="2" t="inlineStr"/>
+      <c r="Q104" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R104" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
@@ -7487,8 +8311,16 @@
       </c>
       <c r="O105" s="2" t="inlineStr"/>
       <c r="P105" s="2" t="inlineStr"/>
-      <c r="Q105" s="2" t="inlineStr"/>
-      <c r="R105" s="2" t="inlineStr"/>
+      <c r="Q105" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R105" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
@@ -7547,8 +8379,16 @@
       <c r="N106" s="2" t="inlineStr"/>
       <c r="O106" s="2" t="inlineStr"/>
       <c r="P106" s="2" t="inlineStr"/>
-      <c r="Q106" s="2" t="inlineStr"/>
-      <c r="R106" s="2" t="inlineStr"/>
+      <c r="Q106" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R106" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
@@ -7619,8 +8459,16 @@
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr"/>
-      <c r="Q107" s="2" t="inlineStr"/>
-      <c r="R107" s="2" t="inlineStr"/>
+      <c r="Q107" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R107" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
@@ -7679,8 +8527,16 @@
       <c r="N108" s="2" t="inlineStr"/>
       <c r="O108" s="2" t="inlineStr"/>
       <c r="P108" s="2" t="inlineStr"/>
-      <c r="Q108" s="2" t="inlineStr"/>
-      <c r="R108" s="2" t="inlineStr"/>
+      <c r="Q108" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R108" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
@@ -7739,8 +8595,16 @@
       <c r="N109" s="2" t="inlineStr"/>
       <c r="O109" s="2" t="inlineStr"/>
       <c r="P109" s="2" t="inlineStr"/>
-      <c r="Q109" s="2" t="inlineStr"/>
-      <c r="R109" s="2" t="inlineStr"/>
+      <c r="Q109" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R109" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
@@ -7803,8 +8667,16 @@
         </is>
       </c>
       <c r="P110" s="2" t="inlineStr"/>
-      <c r="Q110" s="2" t="inlineStr"/>
-      <c r="R110" s="2" t="inlineStr"/>
+      <c r="Q110" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R110" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
@@ -7863,8 +8735,16 @@
       <c r="N111" s="2" t="inlineStr"/>
       <c r="O111" s="2" t="inlineStr"/>
       <c r="P111" s="2" t="inlineStr"/>
-      <c r="Q111" s="2" t="inlineStr"/>
-      <c r="R111" s="2" t="inlineStr"/>
+      <c r="Q111" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R111" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
@@ -7927,8 +8807,16 @@
       <c r="N112" s="2" t="inlineStr"/>
       <c r="O112" s="2" t="inlineStr"/>
       <c r="P112" s="2" t="inlineStr"/>
-      <c r="Q112" s="2" t="inlineStr"/>
-      <c r="R112" s="2" t="inlineStr"/>
+      <c r="Q112" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R112" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
@@ -7987,8 +8875,16 @@
       <c r="N113" s="2" t="inlineStr"/>
       <c r="O113" s="2" t="inlineStr"/>
       <c r="P113" s="2" t="inlineStr"/>
-      <c r="Q113" s="2" t="inlineStr"/>
-      <c r="R113" s="2" t="inlineStr"/>
+      <c r="Q113" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R113" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
@@ -8051,8 +8947,16 @@
         </is>
       </c>
       <c r="P114" s="2" t="inlineStr"/>
-      <c r="Q114" s="2" t="inlineStr"/>
-      <c r="R114" s="2" t="inlineStr"/>
+      <c r="Q114" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R114" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
@@ -8111,8 +9015,16 @@
       <c r="N115" s="2" t="inlineStr"/>
       <c r="O115" s="2" t="inlineStr"/>
       <c r="P115" s="2" t="inlineStr"/>
-      <c r="Q115" s="2" t="inlineStr"/>
-      <c r="R115" s="2" t="inlineStr"/>
+      <c r="Q115" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R115" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
@@ -8171,8 +9083,16 @@
       <c r="N116" s="2" t="inlineStr"/>
       <c r="O116" s="2" t="inlineStr"/>
       <c r="P116" s="2" t="inlineStr"/>
-      <c r="Q116" s="2" t="inlineStr"/>
-      <c r="R116" s="2" t="inlineStr"/>
+      <c r="Q116" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R116" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
@@ -8243,8 +9163,16 @@
         </is>
       </c>
       <c r="P117" s="2" t="inlineStr"/>
-      <c r="Q117" s="2" t="inlineStr"/>
-      <c r="R117" s="2" t="inlineStr"/>
+      <c r="Q117" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R117" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
@@ -8303,8 +9231,16 @@
       <c r="N118" s="2" t="inlineStr"/>
       <c r="O118" s="2" t="inlineStr"/>
       <c r="P118" s="2" t="inlineStr"/>
-      <c r="Q118" s="2" t="inlineStr"/>
-      <c r="R118" s="2" t="inlineStr"/>
+      <c r="Q118" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R118" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
@@ -8371,8 +9307,16 @@
       </c>
       <c r="O119" s="2" t="inlineStr"/>
       <c r="P119" s="2" t="inlineStr"/>
-      <c r="Q119" s="2" t="inlineStr"/>
-      <c r="R119" s="2" t="inlineStr"/>
+      <c r="Q119" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R119" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
@@ -8431,8 +9375,16 @@
       <c r="N120" s="2" t="inlineStr"/>
       <c r="O120" s="2" t="inlineStr"/>
       <c r="P120" s="2" t="inlineStr"/>
-      <c r="Q120" s="2" t="inlineStr"/>
-      <c r="R120" s="2" t="inlineStr"/>
+      <c r="Q120" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R120" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
@@ -8495,8 +9447,16 @@
         </is>
       </c>
       <c r="P121" s="2" t="inlineStr"/>
-      <c r="Q121" s="2" t="inlineStr"/>
-      <c r="R121" s="2" t="inlineStr"/>
+      <c r="Q121" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R121" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
@@ -8555,8 +9515,16 @@
       <c r="N122" s="2" t="inlineStr"/>
       <c r="O122" s="2" t="inlineStr"/>
       <c r="P122" s="2" t="inlineStr"/>
-      <c r="Q122" s="2" t="inlineStr"/>
-      <c r="R122" s="2" t="inlineStr"/>
+      <c r="Q122" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R122" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
@@ -8619,8 +9587,16 @@
       <c r="N123" s="2" t="inlineStr"/>
       <c r="O123" s="2" t="inlineStr"/>
       <c r="P123" s="2" t="inlineStr"/>
-      <c r="Q123" s="2" t="inlineStr"/>
-      <c r="R123" s="2" t="inlineStr"/>
+      <c r="Q123" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R123" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
@@ -8683,8 +9659,16 @@
         </is>
       </c>
       <c r="P124" s="2" t="inlineStr"/>
-      <c r="Q124" s="2" t="inlineStr"/>
-      <c r="R124" s="2" t="inlineStr"/>
+      <c r="Q124" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R124" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
@@ -8743,8 +9727,16 @@
       <c r="N125" s="2" t="inlineStr"/>
       <c r="O125" s="2" t="inlineStr"/>
       <c r="P125" s="2" t="inlineStr"/>
-      <c r="Q125" s="2" t="inlineStr"/>
-      <c r="R125" s="2" t="inlineStr"/>
+      <c r="Q125" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R125" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
@@ -8811,8 +9803,16 @@
       </c>
       <c r="O126" s="2" t="inlineStr"/>
       <c r="P126" s="2" t="inlineStr"/>
-      <c r="Q126" s="2" t="inlineStr"/>
-      <c r="R126" s="2" t="inlineStr"/>
+      <c r="Q126" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R126" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
@@ -8871,8 +9871,16 @@
       <c r="N127" s="2" t="inlineStr"/>
       <c r="O127" s="2" t="inlineStr"/>
       <c r="P127" s="2" t="inlineStr"/>
-      <c r="Q127" s="2" t="inlineStr"/>
-      <c r="R127" s="2" t="inlineStr"/>
+      <c r="Q127" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R127" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
@@ -8939,8 +9947,16 @@
         </is>
       </c>
       <c r="P128" s="2" t="inlineStr"/>
-      <c r="Q128" s="2" t="inlineStr"/>
-      <c r="R128" s="2" t="inlineStr"/>
+      <c r="Q128" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R128" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
@@ -8999,8 +10015,16 @@
       <c r="N129" s="2" t="inlineStr"/>
       <c r="O129" s="2" t="inlineStr"/>
       <c r="P129" s="2" t="inlineStr"/>
-      <c r="Q129" s="2" t="inlineStr"/>
-      <c r="R129" s="2" t="inlineStr"/>
+      <c r="Q129" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R129" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
@@ -9063,8 +10087,16 @@
       <c r="N130" s="2" t="inlineStr"/>
       <c r="O130" s="2" t="inlineStr"/>
       <c r="P130" s="2" t="inlineStr"/>
-      <c r="Q130" s="2" t="inlineStr"/>
-      <c r="R130" s="2" t="inlineStr"/>
+      <c r="Q130" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R130" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
@@ -9135,8 +10167,16 @@
         </is>
       </c>
       <c r="P131" s="2" t="inlineStr"/>
-      <c r="Q131" s="2" t="inlineStr"/>
-      <c r="R131" s="2" t="inlineStr"/>
+      <c r="Q131" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R131" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
@@ -9203,8 +10243,16 @@
       </c>
       <c r="O132" s="2" t="inlineStr"/>
       <c r="P132" s="2" t="inlineStr"/>
-      <c r="Q132" s="2" t="inlineStr"/>
-      <c r="R132" s="2" t="inlineStr"/>
+      <c r="Q132" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R132" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
@@ -9263,8 +10311,16 @@
       <c r="N133" s="2" t="inlineStr"/>
       <c r="O133" s="2" t="inlineStr"/>
       <c r="P133" s="2" t="inlineStr"/>
-      <c r="Q133" s="2" t="inlineStr"/>
-      <c r="R133" s="2" t="inlineStr"/>
+      <c r="Q133" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R133" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
@@ -9323,8 +10379,16 @@
       <c r="N134" s="2" t="inlineStr"/>
       <c r="O134" s="2" t="inlineStr"/>
       <c r="P134" s="2" t="inlineStr"/>
-      <c r="Q134" s="2" t="inlineStr"/>
-      <c r="R134" s="2" t="inlineStr"/>
+      <c r="Q134" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R134" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
@@ -9395,8 +10459,16 @@
         </is>
       </c>
       <c r="P135" s="2" t="inlineStr"/>
-      <c r="Q135" s="2" t="inlineStr"/>
-      <c r="R135" s="2" t="inlineStr"/>
+      <c r="Q135" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R135" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
@@ -9455,8 +10527,16 @@
       <c r="N136" s="2" t="inlineStr"/>
       <c r="O136" s="2" t="inlineStr"/>
       <c r="P136" s="2" t="inlineStr"/>
-      <c r="Q136" s="2" t="inlineStr"/>
-      <c r="R136" s="2" t="inlineStr"/>
+      <c r="Q136" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R136" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
@@ -9519,8 +10599,16 @@
       <c r="N137" s="2" t="inlineStr"/>
       <c r="O137" s="2" t="inlineStr"/>
       <c r="P137" s="2" t="inlineStr"/>
-      <c r="Q137" s="2" t="inlineStr"/>
-      <c r="R137" s="2" t="inlineStr"/>
+      <c r="Q137" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R137" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
@@ -9583,8 +10671,16 @@
         </is>
       </c>
       <c r="P138" s="2" t="inlineStr"/>
-      <c r="Q138" s="2" t="inlineStr"/>
-      <c r="R138" s="2" t="inlineStr"/>
+      <c r="Q138" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R138" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
@@ -9643,8 +10739,16 @@
       <c r="N139" s="2" t="inlineStr"/>
       <c r="O139" s="2" t="inlineStr"/>
       <c r="P139" s="2" t="inlineStr"/>
-      <c r="Q139" s="2" t="inlineStr"/>
-      <c r="R139" s="2" t="inlineStr"/>
+      <c r="Q139" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R139" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
@@ -9711,8 +10815,16 @@
       </c>
       <c r="O140" s="2" t="inlineStr"/>
       <c r="P140" s="2" t="inlineStr"/>
-      <c r="Q140" s="2" t="inlineStr"/>
-      <c r="R140" s="2" t="inlineStr"/>
+      <c r="Q140" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R140" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
@@ -9771,8 +10883,16 @@
       <c r="N141" s="2" t="inlineStr"/>
       <c r="O141" s="2" t="inlineStr"/>
       <c r="P141" s="2" t="inlineStr"/>
-      <c r="Q141" s="2" t="inlineStr"/>
-      <c r="R141" s="2" t="inlineStr"/>
+      <c r="Q141" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R141" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
@@ -9839,8 +10959,16 @@
         </is>
       </c>
       <c r="P142" s="2" t="inlineStr"/>
-      <c r="Q142" s="2" t="inlineStr"/>
-      <c r="R142" s="2" t="inlineStr"/>
+      <c r="Q142" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R142" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
@@ -9899,8 +11027,16 @@
       <c r="N143" s="2" t="inlineStr"/>
       <c r="O143" s="2" t="inlineStr"/>
       <c r="P143" s="2" t="inlineStr"/>
-      <c r="Q143" s="2" t="inlineStr"/>
-      <c r="R143" s="2" t="inlineStr"/>
+      <c r="Q143" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R143" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
@@ -9959,8 +11095,16 @@
       <c r="N144" s="2" t="inlineStr"/>
       <c r="O144" s="2" t="inlineStr"/>
       <c r="P144" s="2" t="inlineStr"/>
-      <c r="Q144" s="2" t="inlineStr"/>
-      <c r="R144" s="2" t="inlineStr"/>
+      <c r="Q144" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R144" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
@@ -10023,8 +11167,16 @@
         </is>
       </c>
       <c r="P145" s="2" t="inlineStr"/>
-      <c r="Q145" s="2" t="inlineStr"/>
-      <c r="R145" s="2" t="inlineStr"/>
+      <c r="Q145" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R145" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
@@ -10087,8 +11239,16 @@
       <c r="N146" s="2" t="inlineStr"/>
       <c r="O146" s="2" t="inlineStr"/>
       <c r="P146" s="2" t="inlineStr"/>
-      <c r="Q146" s="2" t="inlineStr"/>
-      <c r="R146" s="2" t="inlineStr"/>
+      <c r="Q146" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R146" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
@@ -10155,8 +11315,16 @@
       </c>
       <c r="O147" s="2" t="inlineStr"/>
       <c r="P147" s="2" t="inlineStr"/>
-      <c r="Q147" s="2" t="inlineStr"/>
-      <c r="R147" s="2" t="inlineStr"/>
+      <c r="Q147" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R147" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
@@ -10219,8 +11387,16 @@
       </c>
       <c r="O148" s="2" t="inlineStr"/>
       <c r="P148" s="2" t="inlineStr"/>
-      <c r="Q148" s="2" t="inlineStr"/>
-      <c r="R148" s="2" t="inlineStr"/>
+      <c r="Q148" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R148" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
@@ -10287,8 +11463,16 @@
         </is>
       </c>
       <c r="P149" s="2" t="inlineStr"/>
-      <c r="Q149" s="2" t="inlineStr"/>
-      <c r="R149" s="2" t="inlineStr"/>
+      <c r="Q149" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R149" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
@@ -10347,8 +11531,16 @@
       <c r="N150" s="2" t="inlineStr"/>
       <c r="O150" s="2" t="inlineStr"/>
       <c r="P150" s="2" t="inlineStr"/>
-      <c r="Q150" s="2" t="inlineStr"/>
-      <c r="R150" s="2" t="inlineStr"/>
+      <c r="Q150" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R150" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
@@ -10407,8 +11599,16 @@
       <c r="N151" s="2" t="inlineStr"/>
       <c r="O151" s="2" t="inlineStr"/>
       <c r="P151" s="2" t="inlineStr"/>
-      <c r="Q151" s="2" t="inlineStr"/>
-      <c r="R151" s="2" t="inlineStr"/>
+      <c r="Q151" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R151" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
@@ -10471,8 +11671,16 @@
         </is>
       </c>
       <c r="P152" s="2" t="inlineStr"/>
-      <c r="Q152" s="2" t="inlineStr"/>
-      <c r="R152" s="2" t="inlineStr"/>
+      <c r="Q152" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R152" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
@@ -10531,8 +11739,16 @@
       <c r="N153" s="2" t="inlineStr"/>
       <c r="O153" s="2" t="inlineStr"/>
       <c r="P153" s="2" t="inlineStr"/>
-      <c r="Q153" s="2" t="inlineStr"/>
-      <c r="R153" s="2" t="inlineStr"/>
+      <c r="Q153" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R153" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
@@ -10591,8 +11807,16 @@
       <c r="N154" s="2" t="inlineStr"/>
       <c r="O154" s="2" t="inlineStr"/>
       <c r="P154" s="2" t="inlineStr"/>
-      <c r="Q154" s="2" t="inlineStr"/>
-      <c r="R154" s="2" t="inlineStr"/>
+      <c r="Q154" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R154" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
@@ -10651,8 +11875,16 @@
       <c r="N155" s="2" t="inlineStr"/>
       <c r="O155" s="2" t="inlineStr"/>
       <c r="P155" s="2" t="inlineStr"/>
-      <c r="Q155" s="2" t="inlineStr"/>
-      <c r="R155" s="2" t="inlineStr"/>
+      <c r="Q155" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R155" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
@@ -10715,8 +11947,16 @@
         </is>
       </c>
       <c r="P156" s="2" t="inlineStr"/>
-      <c r="Q156" s="2" t="inlineStr"/>
-      <c r="R156" s="2" t="inlineStr"/>
+      <c r="Q156" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R156" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
@@ -10775,8 +12015,16 @@
       <c r="N157" s="2" t="inlineStr"/>
       <c r="O157" s="2" t="inlineStr"/>
       <c r="P157" s="2" t="inlineStr"/>
-      <c r="Q157" s="2" t="inlineStr"/>
-      <c r="R157" s="2" t="inlineStr"/>
+      <c r="Q157" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R157" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
@@ -10835,8 +12083,16 @@
       <c r="N158" s="2" t="inlineStr"/>
       <c r="O158" s="2" t="inlineStr"/>
       <c r="P158" s="2" t="inlineStr"/>
-      <c r="Q158" s="2" t="inlineStr"/>
-      <c r="R158" s="2" t="inlineStr"/>
+      <c r="Q158" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R158" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
@@ -10903,8 +12159,16 @@
         </is>
       </c>
       <c r="P159" s="2" t="inlineStr"/>
-      <c r="Q159" s="2" t="inlineStr"/>
-      <c r="R159" s="2" t="inlineStr"/>
+      <c r="Q159" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R159" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
@@ -10963,8 +12227,16 @@
       <c r="N160" s="2" t="inlineStr"/>
       <c r="O160" s="2" t="inlineStr"/>
       <c r="P160" s="2" t="inlineStr"/>
-      <c r="Q160" s="2" t="inlineStr"/>
-      <c r="R160" s="2" t="inlineStr"/>
+      <c r="Q160" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R160" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
@@ -11031,8 +12303,16 @@
       </c>
       <c r="O161" s="2" t="inlineStr"/>
       <c r="P161" s="2" t="inlineStr"/>
-      <c r="Q161" s="2" t="inlineStr"/>
-      <c r="R161" s="2" t="inlineStr"/>
+      <c r="Q161" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R161" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
@@ -11091,8 +12371,16 @@
       <c r="N162" s="2" t="inlineStr"/>
       <c r="O162" s="2" t="inlineStr"/>
       <c r="P162" s="2" t="inlineStr"/>
-      <c r="Q162" s="2" t="inlineStr"/>
-      <c r="R162" s="2" t="inlineStr"/>
+      <c r="Q162" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R162" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
@@ -11155,8 +12443,16 @@
         </is>
       </c>
       <c r="P163" s="2" t="inlineStr"/>
-      <c r="Q163" s="2" t="inlineStr"/>
-      <c r="R163" s="2" t="inlineStr"/>
+      <c r="Q163" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R163" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
@@ -11215,8 +12511,16 @@
       <c r="N164" s="2" t="inlineStr"/>
       <c r="O164" s="2" t="inlineStr"/>
       <c r="P164" s="2" t="inlineStr"/>
-      <c r="Q164" s="2" t="inlineStr"/>
-      <c r="R164" s="2" t="inlineStr"/>
+      <c r="Q164" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R164" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
@@ -11275,8 +12579,16 @@
       <c r="N165" s="2" t="inlineStr"/>
       <c r="O165" s="2" t="inlineStr"/>
       <c r="P165" s="2" t="inlineStr"/>
-      <c r="Q165" s="2" t="inlineStr"/>
-      <c r="R165" s="2" t="inlineStr"/>
+      <c r="Q165" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R165" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
@@ -11335,8 +12647,16 @@
       <c r="N166" s="2" t="inlineStr"/>
       <c r="O166" s="2" t="inlineStr"/>
       <c r="P166" s="2" t="inlineStr"/>
-      <c r="Q166" s="2" t="inlineStr"/>
-      <c r="R166" s="2" t="inlineStr"/>
+      <c r="Q166" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R166" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
@@ -11395,8 +12715,16 @@
       <c r="N167" s="2" t="inlineStr"/>
       <c r="O167" s="2" t="inlineStr"/>
       <c r="P167" s="2" t="inlineStr"/>
-      <c r="Q167" s="2" t="inlineStr"/>
-      <c r="R167" s="2" t="inlineStr"/>
+      <c r="Q167" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R167" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
@@ -11463,8 +12791,16 @@
       </c>
       <c r="O168" s="2" t="inlineStr"/>
       <c r="P168" s="2" t="inlineStr"/>
-      <c r="Q168" s="2" t="inlineStr"/>
-      <c r="R168" s="2" t="inlineStr"/>
+      <c r="Q168" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R168" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
@@ -11523,8 +12859,16 @@
       <c r="N169" s="2" t="inlineStr"/>
       <c r="O169" s="2" t="inlineStr"/>
       <c r="P169" s="2" t="inlineStr"/>
-      <c r="Q169" s="2" t="inlineStr"/>
-      <c r="R169" s="2" t="inlineStr"/>
+      <c r="Q169" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R169" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
@@ -11587,8 +12931,16 @@
       <c r="N170" s="2" t="inlineStr"/>
       <c r="O170" s="2" t="inlineStr"/>
       <c r="P170" s="2" t="inlineStr"/>
-      <c r="Q170" s="2" t="inlineStr"/>
-      <c r="R170" s="2" t="inlineStr"/>
+      <c r="Q170" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R170" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
@@ -11651,8 +13003,16 @@
       </c>
       <c r="O171" s="2" t="inlineStr"/>
       <c r="P171" s="2" t="inlineStr"/>
-      <c r="Q171" s="2" t="inlineStr"/>
-      <c r="R171" s="2" t="inlineStr"/>
+      <c r="Q171" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R171" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
@@ -11711,8 +13071,16 @@
       <c r="N172" s="2" t="inlineStr"/>
       <c r="O172" s="2" t="inlineStr"/>
       <c r="P172" s="2" t="inlineStr"/>
-      <c r="Q172" s="2" t="inlineStr"/>
-      <c r="R172" s="2" t="inlineStr"/>
+      <c r="Q172" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R172" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
@@ -11779,8 +13147,16 @@
       </c>
       <c r="O173" s="2" t="inlineStr"/>
       <c r="P173" s="2" t="inlineStr"/>
-      <c r="Q173" s="2" t="inlineStr"/>
-      <c r="R173" s="2" t="inlineStr"/>
+      <c r="Q173" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R173" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
@@ -11839,8 +13215,16 @@
       <c r="N174" s="2" t="inlineStr"/>
       <c r="O174" s="2" t="inlineStr"/>
       <c r="P174" s="2" t="inlineStr"/>
-      <c r="Q174" s="2" t="inlineStr"/>
-      <c r="R174" s="2" t="inlineStr"/>
+      <c r="Q174" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R174" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
@@ -11899,8 +13283,16 @@
       <c r="N175" s="2" t="inlineStr"/>
       <c r="O175" s="2" t="inlineStr"/>
       <c r="P175" s="2" t="inlineStr"/>
-      <c r="Q175" s="2" t="inlineStr"/>
-      <c r="R175" s="2" t="inlineStr"/>
+      <c r="Q175" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R175" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
@@ -11967,8 +13359,16 @@
       </c>
       <c r="O176" s="2" t="inlineStr"/>
       <c r="P176" s="2" t="inlineStr"/>
-      <c r="Q176" s="2" t="inlineStr"/>
-      <c r="R176" s="2" t="inlineStr"/>
+      <c r="Q176" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R176" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
@@ -12031,8 +13431,16 @@
       <c r="N177" s="2" t="inlineStr"/>
       <c r="O177" s="2" t="inlineStr"/>
       <c r="P177" s="2" t="inlineStr"/>
-      <c r="Q177" s="2" t="inlineStr"/>
-      <c r="R177" s="2" t="inlineStr"/>
+      <c r="Q177" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R177" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
@@ -12091,8 +13499,16 @@
       <c r="N178" s="2" t="inlineStr"/>
       <c r="O178" s="2" t="inlineStr"/>
       <c r="P178" s="2" t="inlineStr"/>
-      <c r="Q178" s="2" t="inlineStr"/>
-      <c r="R178" s="2" t="inlineStr"/>
+      <c r="Q178" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R178" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
@@ -12151,8 +13567,16 @@
       <c r="N179" s="2" t="inlineStr"/>
       <c r="O179" s="2" t="inlineStr"/>
       <c r="P179" s="2" t="inlineStr"/>
-      <c r="Q179" s="2" t="inlineStr"/>
-      <c r="R179" s="2" t="inlineStr"/>
+      <c r="Q179" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R179" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
@@ -12215,8 +13639,16 @@
       <c r="N180" s="2" t="inlineStr"/>
       <c r="O180" s="2" t="inlineStr"/>
       <c r="P180" s="2" t="inlineStr"/>
-      <c r="Q180" s="2" t="inlineStr"/>
-      <c r="R180" s="2" t="inlineStr"/>
+      <c r="Q180" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R180" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
@@ -12275,8 +13707,16 @@
       <c r="N181" s="2" t="inlineStr"/>
       <c r="O181" s="2" t="inlineStr"/>
       <c r="P181" s="2" t="inlineStr"/>
-      <c r="Q181" s="2" t="inlineStr"/>
-      <c r="R181" s="2" t="inlineStr"/>
+      <c r="Q181" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R181" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
@@ -12343,8 +13783,16 @@
       </c>
       <c r="O182" s="2" t="inlineStr"/>
       <c r="P182" s="2" t="inlineStr"/>
-      <c r="Q182" s="2" t="inlineStr"/>
-      <c r="R182" s="2" t="inlineStr"/>
+      <c r="Q182" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R182" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
@@ -12403,8 +13851,16 @@
       <c r="N183" s="2" t="inlineStr"/>
       <c r="O183" s="2" t="inlineStr"/>
       <c r="P183" s="2" t="inlineStr"/>
-      <c r="Q183" s="2" t="inlineStr"/>
-      <c r="R183" s="2" t="inlineStr"/>
+      <c r="Q183" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R183" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
@@ -12475,8 +13931,16 @@
       </c>
       <c r="O184" s="2" t="inlineStr"/>
       <c r="P184" s="2" t="inlineStr"/>
-      <c r="Q184" s="2" t="inlineStr"/>
-      <c r="R184" s="2" t="inlineStr"/>
+      <c r="Q184" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R184" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
@@ -12535,8 +13999,16 @@
       <c r="N185" s="2" t="inlineStr"/>
       <c r="O185" s="2" t="inlineStr"/>
       <c r="P185" s="2" t="inlineStr"/>
-      <c r="Q185" s="2" t="inlineStr"/>
-      <c r="R185" s="2" t="inlineStr"/>
+      <c r="Q185" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R185" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
@@ -12599,8 +14071,16 @@
       </c>
       <c r="O186" s="2" t="inlineStr"/>
       <c r="P186" s="2" t="inlineStr"/>
-      <c r="Q186" s="2" t="inlineStr"/>
-      <c r="R186" s="2" t="inlineStr"/>
+      <c r="Q186" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R186" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
@@ -12663,8 +14143,16 @@
       <c r="N187" s="2" t="inlineStr"/>
       <c r="O187" s="2" t="inlineStr"/>
       <c r="P187" s="2" t="inlineStr"/>
-      <c r="Q187" s="2" t="inlineStr"/>
-      <c r="R187" s="2" t="inlineStr"/>
+      <c r="Q187" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R187" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
@@ -12727,8 +14215,16 @@
       </c>
       <c r="O188" s="2" t="inlineStr"/>
       <c r="P188" s="2" t="inlineStr"/>
-      <c r="Q188" s="2" t="inlineStr"/>
-      <c r="R188" s="2" t="inlineStr"/>
+      <c r="Q188" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R188" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
@@ -12795,8 +14291,16 @@
       </c>
       <c r="O189" s="2" t="inlineStr"/>
       <c r="P189" s="2" t="inlineStr"/>
-      <c r="Q189" s="2" t="inlineStr"/>
-      <c r="R189" s="2" t="inlineStr"/>
+      <c r="Q189" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R189" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
@@ -12855,8 +14359,16 @@
       <c r="N190" s="2" t="inlineStr"/>
       <c r="O190" s="2" t="inlineStr"/>
       <c r="P190" s="2" t="inlineStr"/>
-      <c r="Q190" s="2" t="inlineStr"/>
-      <c r="R190" s="2" t="inlineStr"/>
+      <c r="Q190" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R190" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
@@ -12915,8 +14427,16 @@
       <c r="N191" s="2" t="inlineStr"/>
       <c r="O191" s="2" t="inlineStr"/>
       <c r="P191" s="2" t="inlineStr"/>
-      <c r="Q191" s="2" t="inlineStr"/>
-      <c r="R191" s="2" t="inlineStr"/>
+      <c r="Q191" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R191" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
@@ -12975,8 +14495,16 @@
       <c r="N192" s="2" t="inlineStr"/>
       <c r="O192" s="2" t="inlineStr"/>
       <c r="P192" s="2" t="inlineStr"/>
-      <c r="Q192" s="2" t="inlineStr"/>
-      <c r="R192" s="2" t="inlineStr"/>
+      <c r="Q192" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R192" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
@@ -13035,8 +14563,16 @@
       <c r="N193" s="2" t="inlineStr"/>
       <c r="O193" s="2" t="inlineStr"/>
       <c r="P193" s="2" t="inlineStr"/>
-      <c r="Q193" s="2" t="inlineStr"/>
-      <c r="R193" s="2" t="inlineStr"/>
+      <c r="Q193" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R193" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
@@ -13095,8 +14631,16 @@
       <c r="N194" s="2" t="inlineStr"/>
       <c r="O194" s="2" t="inlineStr"/>
       <c r="P194" s="2" t="inlineStr"/>
-      <c r="Q194" s="2" t="inlineStr"/>
-      <c r="R194" s="2" t="inlineStr"/>
+      <c r="Q194" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R194" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
@@ -13155,8 +14699,16 @@
       <c r="N195" s="2" t="inlineStr"/>
       <c r="O195" s="2" t="inlineStr"/>
       <c r="P195" s="2" t="inlineStr"/>
-      <c r="Q195" s="2" t="inlineStr"/>
-      <c r="R195" s="2" t="inlineStr"/>
+      <c r="Q195" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R195" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
@@ -13215,8 +14767,16 @@
       <c r="N196" s="2" t="inlineStr"/>
       <c r="O196" s="2" t="inlineStr"/>
       <c r="P196" s="2" t="inlineStr"/>
-      <c r="Q196" s="2" t="inlineStr"/>
-      <c r="R196" s="2" t="inlineStr"/>
+      <c r="Q196" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R196" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
@@ -13275,8 +14835,16 @@
       <c r="N197" s="2" t="inlineStr"/>
       <c r="O197" s="2" t="inlineStr"/>
       <c r="P197" s="2" t="inlineStr"/>
-      <c r="Q197" s="2" t="inlineStr"/>
-      <c r="R197" s="2" t="inlineStr"/>
+      <c r="Q197" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R197" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
@@ -13335,8 +14903,16 @@
       <c r="N198" s="2" t="inlineStr"/>
       <c r="O198" s="2" t="inlineStr"/>
       <c r="P198" s="2" t="inlineStr"/>
-      <c r="Q198" s="2" t="inlineStr"/>
-      <c r="R198" s="2" t="inlineStr"/>
+      <c r="Q198" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R198" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
@@ -13395,8 +14971,16 @@
       <c r="N199" s="2" t="inlineStr"/>
       <c r="O199" s="2" t="inlineStr"/>
       <c r="P199" s="2" t="inlineStr"/>
-      <c r="Q199" s="2" t="inlineStr"/>
-      <c r="R199" s="2" t="inlineStr"/>
+      <c r="Q199" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R199" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
@@ -13455,8 +15039,16 @@
       <c r="N200" s="2" t="inlineStr"/>
       <c r="O200" s="2" t="inlineStr"/>
       <c r="P200" s="2" t="inlineStr"/>
-      <c r="Q200" s="2" t="inlineStr"/>
-      <c r="R200" s="2" t="inlineStr"/>
+      <c r="Q200" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R200" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
@@ -13515,8 +15107,16 @@
       <c r="N201" s="2" t="inlineStr"/>
       <c r="O201" s="2" t="inlineStr"/>
       <c r="P201" s="2" t="inlineStr"/>
-      <c r="Q201" s="2" t="inlineStr"/>
-      <c r="R201" s="2" t="inlineStr"/>
+      <c r="Q201" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R201" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
@@ -13583,8 +15183,16 @@
       </c>
       <c r="O202" s="2" t="inlineStr"/>
       <c r="P202" s="2" t="inlineStr"/>
-      <c r="Q202" s="2" t="inlineStr"/>
-      <c r="R202" s="2" t="inlineStr"/>
+      <c r="Q202" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R202" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
@@ -13651,8 +15259,16 @@
       </c>
       <c r="O203" s="2" t="inlineStr"/>
       <c r="P203" s="2" t="inlineStr"/>
-      <c r="Q203" s="2" t="inlineStr"/>
-      <c r="R203" s="2" t="inlineStr"/>
+      <c r="Q203" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R203" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
@@ -13711,8 +15327,16 @@
       <c r="N204" s="2" t="inlineStr"/>
       <c r="O204" s="2" t="inlineStr"/>
       <c r="P204" s="2" t="inlineStr"/>
-      <c r="Q204" s="2" t="inlineStr"/>
-      <c r="R204" s="2" t="inlineStr"/>
+      <c r="Q204" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R204" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
@@ -13775,8 +15399,16 @@
       <c r="N205" s="2" t="inlineStr"/>
       <c r="O205" s="2" t="inlineStr"/>
       <c r="P205" s="2" t="inlineStr"/>
-      <c r="Q205" s="2" t="inlineStr"/>
-      <c r="R205" s="2" t="inlineStr"/>
+      <c r="Q205" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R205" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
@@ -13835,8 +15467,16 @@
       <c r="N206" s="2" t="inlineStr"/>
       <c r="O206" s="2" t="inlineStr"/>
       <c r="P206" s="2" t="inlineStr"/>
-      <c r="Q206" s="2" t="inlineStr"/>
-      <c r="R206" s="2" t="inlineStr"/>
+      <c r="Q206" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R206" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
@@ -13895,8 +15535,16 @@
       <c r="N207" s="2" t="inlineStr"/>
       <c r="O207" s="2" t="inlineStr"/>
       <c r="P207" s="2" t="inlineStr"/>
-      <c r="Q207" s="2" t="inlineStr"/>
-      <c r="R207" s="2" t="inlineStr"/>
+      <c r="Q207" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R207" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
@@ -13955,8 +15603,16 @@
       <c r="N208" s="2" t="inlineStr"/>
       <c r="O208" s="2" t="inlineStr"/>
       <c r="P208" s="2" t="inlineStr"/>
-      <c r="Q208" s="2" t="inlineStr"/>
-      <c r="R208" s="2" t="inlineStr"/>
+      <c r="Q208" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R208" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
@@ -14015,8 +15671,16 @@
       <c r="N209" s="2" t="inlineStr"/>
       <c r="O209" s="2" t="inlineStr"/>
       <c r="P209" s="2" t="inlineStr"/>
-      <c r="Q209" s="2" t="inlineStr"/>
-      <c r="R209" s="2" t="inlineStr"/>
+      <c r="Q209" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R209" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
@@ -14083,8 +15747,16 @@
       </c>
       <c r="O210" s="2" t="inlineStr"/>
       <c r="P210" s="2" t="inlineStr"/>
-      <c r="Q210" s="2" t="inlineStr"/>
-      <c r="R210" s="2" t="inlineStr"/>
+      <c r="Q210" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R210" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
@@ -14143,8 +15815,16 @@
       <c r="N211" s="2" t="inlineStr"/>
       <c r="O211" s="2" t="inlineStr"/>
       <c r="P211" s="2" t="inlineStr"/>
-      <c r="Q211" s="2" t="inlineStr"/>
-      <c r="R211" s="2" t="inlineStr"/>
+      <c r="Q211" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R211" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
@@ -14207,8 +15887,16 @@
       </c>
       <c r="O212" s="2" t="inlineStr"/>
       <c r="P212" s="2" t="inlineStr"/>
-      <c r="Q212" s="2" t="inlineStr"/>
-      <c r="R212" s="2" t="inlineStr"/>
+      <c r="Q212" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R212" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
@@ -14267,8 +15955,16 @@
       <c r="N213" s="2" t="inlineStr"/>
       <c r="O213" s="2" t="inlineStr"/>
       <c r="P213" s="2" t="inlineStr"/>
-      <c r="Q213" s="2" t="inlineStr"/>
-      <c r="R213" s="2" t="inlineStr"/>
+      <c r="Q213" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R213" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
@@ -14327,8 +16023,16 @@
       <c r="N214" s="2" t="inlineStr"/>
       <c r="O214" s="2" t="inlineStr"/>
       <c r="P214" s="2" t="inlineStr"/>
-      <c r="Q214" s="2" t="inlineStr"/>
-      <c r="R214" s="2" t="inlineStr"/>
+      <c r="Q214" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R214" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
@@ -14399,8 +16103,16 @@
       </c>
       <c r="O215" s="2" t="inlineStr"/>
       <c r="P215" s="2" t="inlineStr"/>
-      <c r="Q215" s="2" t="inlineStr"/>
-      <c r="R215" s="2" t="inlineStr"/>
+      <c r="Q215" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R215" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
@@ -14467,8 +16179,16 @@
       </c>
       <c r="O216" s="2" t="inlineStr"/>
       <c r="P216" s="2" t="inlineStr"/>
-      <c r="Q216" s="2" t="inlineStr"/>
-      <c r="R216" s="2" t="inlineStr"/>
+      <c r="Q216" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R216" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
@@ -14535,8 +16255,16 @@
       </c>
       <c r="O217" s="2" t="inlineStr"/>
       <c r="P217" s="2" t="inlineStr"/>
-      <c r="Q217" s="2" t="inlineStr"/>
-      <c r="R217" s="2" t="inlineStr"/>
+      <c r="Q217" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R217" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
@@ -14599,8 +16327,16 @@
       </c>
       <c r="O218" s="2" t="inlineStr"/>
       <c r="P218" s="2" t="inlineStr"/>
-      <c r="Q218" s="2" t="inlineStr"/>
-      <c r="R218" s="2" t="inlineStr"/>
+      <c r="Q218" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R218" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
@@ -14659,8 +16395,16 @@
       <c r="N219" s="2" t="inlineStr"/>
       <c r="O219" s="2" t="inlineStr"/>
       <c r="P219" s="2" t="inlineStr"/>
-      <c r="Q219" s="2" t="inlineStr"/>
-      <c r="R219" s="2" t="inlineStr"/>
+      <c r="Q219" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R219" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
@@ -14719,8 +16463,16 @@
       <c r="N220" s="2" t="inlineStr"/>
       <c r="O220" s="2" t="inlineStr"/>
       <c r="P220" s="2" t="inlineStr"/>
-      <c r="Q220" s="2" t="inlineStr"/>
-      <c r="R220" s="2" t="inlineStr"/>
+      <c r="Q220" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R220" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
@@ -14783,8 +16535,16 @@
       <c r="N221" s="2" t="inlineStr"/>
       <c r="O221" s="2" t="inlineStr"/>
       <c r="P221" s="2" t="inlineStr"/>
-      <c r="Q221" s="2" t="inlineStr"/>
-      <c r="R221" s="2" t="inlineStr"/>
+      <c r="Q221" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R221" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
@@ -14851,8 +16611,16 @@
       </c>
       <c r="O222" s="2" t="inlineStr"/>
       <c r="P222" s="2" t="inlineStr"/>
-      <c r="Q222" s="2" t="inlineStr"/>
-      <c r="R222" s="2" t="inlineStr"/>
+      <c r="Q222" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R222" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
@@ -14911,8 +16679,16 @@
       <c r="N223" s="2" t="inlineStr"/>
       <c r="O223" s="2" t="inlineStr"/>
       <c r="P223" s="2" t="inlineStr"/>
-      <c r="Q223" s="2" t="inlineStr"/>
-      <c r="R223" s="2" t="inlineStr"/>
+      <c r="Q223" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R223" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
@@ -14971,8 +16747,16 @@
       <c r="N224" s="2" t="inlineStr"/>
       <c r="O224" s="2" t="inlineStr"/>
       <c r="P224" s="2" t="inlineStr"/>
-      <c r="Q224" s="2" t="inlineStr"/>
-      <c r="R224" s="2" t="inlineStr"/>
+      <c r="Q224" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R224" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
@@ -15031,8 +16815,16 @@
       <c r="N225" s="2" t="inlineStr"/>
       <c r="O225" s="2" t="inlineStr"/>
       <c r="P225" s="2" t="inlineStr"/>
-      <c r="Q225" s="2" t="inlineStr"/>
-      <c r="R225" s="2" t="inlineStr"/>
+      <c r="Q225" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R225" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
@@ -15095,8 +16887,16 @@
       </c>
       <c r="O226" s="2" t="inlineStr"/>
       <c r="P226" s="2" t="inlineStr"/>
-      <c r="Q226" s="2" t="inlineStr"/>
-      <c r="R226" s="2" t="inlineStr"/>
+      <c r="Q226" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R226" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
@@ -15155,8 +16955,16 @@
       <c r="N227" s="2" t="inlineStr"/>
       <c r="O227" s="2" t="inlineStr"/>
       <c r="P227" s="2" t="inlineStr"/>
-      <c r="Q227" s="2" t="inlineStr"/>
-      <c r="R227" s="2" t="inlineStr"/>
+      <c r="Q227" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R227" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
@@ -15215,8 +17023,16 @@
       <c r="N228" s="2" t="inlineStr"/>
       <c r="O228" s="2" t="inlineStr"/>
       <c r="P228" s="2" t="inlineStr"/>
-      <c r="Q228" s="2" t="inlineStr"/>
-      <c r="R228" s="2" t="inlineStr"/>
+      <c r="Q228" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R228" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
@@ -15283,8 +17099,16 @@
       </c>
       <c r="O229" s="2" t="inlineStr"/>
       <c r="P229" s="2" t="inlineStr"/>
-      <c r="Q229" s="2" t="inlineStr"/>
-      <c r="R229" s="2" t="inlineStr"/>
+      <c r="Q229" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R229" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
@@ -15343,8 +17167,16 @@
       <c r="N230" s="2" t="inlineStr"/>
       <c r="O230" s="2" t="inlineStr"/>
       <c r="P230" s="2" t="inlineStr"/>
-      <c r="Q230" s="2" t="inlineStr"/>
-      <c r="R230" s="2" t="inlineStr"/>
+      <c r="Q230" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R230" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
@@ -15411,8 +17243,16 @@
       </c>
       <c r="O231" s="2" t="inlineStr"/>
       <c r="P231" s="2" t="inlineStr"/>
-      <c r="Q231" s="2" t="inlineStr"/>
-      <c r="R231" s="2" t="inlineStr"/>
+      <c r="Q231" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R231" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
@@ -15471,8 +17311,16 @@
       <c r="N232" s="2" t="inlineStr"/>
       <c r="O232" s="2" t="inlineStr"/>
       <c r="P232" s="2" t="inlineStr"/>
-      <c r="Q232" s="2" t="inlineStr"/>
-      <c r="R232" s="2" t="inlineStr"/>
+      <c r="Q232" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R232" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
@@ -15535,8 +17383,16 @@
       <c r="N233" s="2" t="inlineStr"/>
       <c r="O233" s="2" t="inlineStr"/>
       <c r="P233" s="2" t="inlineStr"/>
-      <c r="Q233" s="2" t="inlineStr"/>
-      <c r="R233" s="2" t="inlineStr"/>
+      <c r="Q233" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R233" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
@@ -15599,8 +17455,16 @@
       <c r="N234" s="2" t="inlineStr"/>
       <c r="O234" s="2" t="inlineStr"/>
       <c r="P234" s="2" t="inlineStr"/>
-      <c r="Q234" s="2" t="inlineStr"/>
-      <c r="R234" s="2" t="inlineStr"/>
+      <c r="Q234" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R234" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
@@ -15659,8 +17523,16 @@
       <c r="N235" s="2" t="inlineStr"/>
       <c r="O235" s="2" t="inlineStr"/>
       <c r="P235" s="2" t="inlineStr"/>
-      <c r="Q235" s="2" t="inlineStr"/>
-      <c r="R235" s="2" t="inlineStr"/>
+      <c r="Q235" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R235" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
@@ -15727,8 +17599,16 @@
       </c>
       <c r="O236" s="2" t="inlineStr"/>
       <c r="P236" s="2" t="inlineStr"/>
-      <c r="Q236" s="2" t="inlineStr"/>
-      <c r="R236" s="2" t="inlineStr"/>
+      <c r="Q236" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R236" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
@@ -15791,8 +17671,16 @@
       <c r="N237" s="2" t="inlineStr"/>
       <c r="O237" s="2" t="inlineStr"/>
       <c r="P237" s="2" t="inlineStr"/>
-      <c r="Q237" s="2" t="inlineStr"/>
-      <c r="R237" s="2" t="inlineStr"/>
+      <c r="Q237" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R237" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">
@@ -15859,8 +17747,16 @@
       </c>
       <c r="O238" s="2" t="inlineStr"/>
       <c r="P238" s="2" t="inlineStr"/>
-      <c r="Q238" s="2" t="inlineStr"/>
-      <c r="R238" s="2" t="inlineStr"/>
+      <c r="Q238" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R238" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n">
@@ -15919,8 +17815,16 @@
       <c r="N239" s="2" t="inlineStr"/>
       <c r="O239" s="2" t="inlineStr"/>
       <c r="P239" s="2" t="inlineStr"/>
-      <c r="Q239" s="2" t="inlineStr"/>
-      <c r="R239" s="2" t="inlineStr"/>
+      <c r="Q239" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R239" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
@@ -15983,8 +17887,16 @@
       <c r="N240" s="2" t="inlineStr"/>
       <c r="O240" s="2" t="inlineStr"/>
       <c r="P240" s="2" t="inlineStr"/>
-      <c r="Q240" s="2" t="inlineStr"/>
-      <c r="R240" s="2" t="inlineStr"/>
+      <c r="Q240" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R240" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n">
@@ -16043,8 +17955,16 @@
       <c r="N241" s="2" t="inlineStr"/>
       <c r="O241" s="2" t="inlineStr"/>
       <c r="P241" s="2" t="inlineStr"/>
-      <c r="Q241" s="2" t="inlineStr"/>
-      <c r="R241" s="2" t="inlineStr"/>
+      <c r="Q241" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R241" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n">
@@ -16103,8 +18023,16 @@
       <c r="N242" s="2" t="inlineStr"/>
       <c r="O242" s="2" t="inlineStr"/>
       <c r="P242" s="2" t="inlineStr"/>
-      <c r="Q242" s="2" t="inlineStr"/>
-      <c r="R242" s="2" t="inlineStr"/>
+      <c r="Q242" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R242" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="n">
@@ -16171,8 +18099,16 @@
       </c>
       <c r="O243" s="2" t="inlineStr"/>
       <c r="P243" s="2" t="inlineStr"/>
-      <c r="Q243" s="2" t="inlineStr"/>
-      <c r="R243" s="2" t="inlineStr"/>
+      <c r="Q243" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R243" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n">
@@ -16235,8 +18171,16 @@
       <c r="N244" s="2" t="inlineStr"/>
       <c r="O244" s="2" t="inlineStr"/>
       <c r="P244" s="2" t="inlineStr"/>
-      <c r="Q244" s="2" t="inlineStr"/>
-      <c r="R244" s="2" t="inlineStr"/>
+      <c r="Q244" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R244" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n">
@@ -16303,8 +18247,16 @@
       </c>
       <c r="O245" s="2" t="inlineStr"/>
       <c r="P245" s="2" t="inlineStr"/>
-      <c r="Q245" s="2" t="inlineStr"/>
-      <c r="R245" s="2" t="inlineStr"/>
+      <c r="Q245" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R245" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n">
@@ -16363,8 +18315,16 @@
       <c r="N246" s="2" t="inlineStr"/>
       <c r="O246" s="2" t="inlineStr"/>
       <c r="P246" s="2" t="inlineStr"/>
-      <c r="Q246" s="2" t="inlineStr"/>
-      <c r="R246" s="2" t="inlineStr"/>
+      <c r="Q246" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R246" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n">
@@ -16427,8 +18387,16 @@
       </c>
       <c r="O247" s="2" t="inlineStr"/>
       <c r="P247" s="2" t="inlineStr"/>
-      <c r="Q247" s="2" t="inlineStr"/>
-      <c r="R247" s="2" t="inlineStr"/>
+      <c r="Q247" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R247" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n">
@@ -16491,8 +18459,16 @@
       </c>
       <c r="O248" s="2" t="inlineStr"/>
       <c r="P248" s="2" t="inlineStr"/>
-      <c r="Q248" s="2" t="inlineStr"/>
-      <c r="R248" s="2" t="inlineStr"/>
+      <c r="Q248" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R248" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n">
@@ -16551,8 +18527,16 @@
       <c r="N249" s="2" t="inlineStr"/>
       <c r="O249" s="2" t="inlineStr"/>
       <c r="P249" s="2" t="inlineStr"/>
-      <c r="Q249" s="2" t="inlineStr"/>
-      <c r="R249" s="2" t="inlineStr"/>
+      <c r="Q249" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R249" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n">
@@ -16619,8 +18603,16 @@
       </c>
       <c r="O250" s="2" t="inlineStr"/>
       <c r="P250" s="2" t="inlineStr"/>
-      <c r="Q250" s="2" t="inlineStr"/>
-      <c r="R250" s="2" t="inlineStr"/>
+      <c r="Q250" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R250" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n">
@@ -16687,8 +18679,16 @@
       </c>
       <c r="O251" s="2" t="inlineStr"/>
       <c r="P251" s="2" t="inlineStr"/>
-      <c r="Q251" s="2" t="inlineStr"/>
-      <c r="R251" s="2" t="inlineStr"/>
+      <c r="Q251" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R251" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="n">
@@ -16747,8 +18747,16 @@
       <c r="N252" s="2" t="inlineStr"/>
       <c r="O252" s="2" t="inlineStr"/>
       <c r="P252" s="2" t="inlineStr"/>
-      <c r="Q252" s="2" t="inlineStr"/>
-      <c r="R252" s="2" t="inlineStr"/>
+      <c r="Q252" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R252" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="n">
@@ -16807,8 +18815,16 @@
       <c r="N253" s="2" t="inlineStr"/>
       <c r="O253" s="2" t="inlineStr"/>
       <c r="P253" s="2" t="inlineStr"/>
-      <c r="Q253" s="2" t="inlineStr"/>
-      <c r="R253" s="2" t="inlineStr"/>
+      <c r="Q253" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R253" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="n">
@@ -16867,8 +18883,16 @@
       <c r="N254" s="2" t="inlineStr"/>
       <c r="O254" s="2" t="inlineStr"/>
       <c r="P254" s="2" t="inlineStr"/>
-      <c r="Q254" s="2" t="inlineStr"/>
-      <c r="R254" s="2" t="inlineStr"/>
+      <c r="Q254" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R254" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="n">
@@ -16927,8 +18951,16 @@
       <c r="N255" s="2" t="inlineStr"/>
       <c r="O255" s="2" t="inlineStr"/>
       <c r="P255" s="2" t="inlineStr"/>
-      <c r="Q255" s="2" t="inlineStr"/>
-      <c r="R255" s="2" t="inlineStr"/>
+      <c r="Q255" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R255" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="n">
@@ -16987,8 +19019,16 @@
       <c r="N256" s="2" t="inlineStr"/>
       <c r="O256" s="2" t="inlineStr"/>
       <c r="P256" s="2" t="inlineStr"/>
-      <c r="Q256" s="2" t="inlineStr"/>
-      <c r="R256" s="2" t="inlineStr"/>
+      <c r="Q256" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R256" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="n">
@@ -17055,8 +19095,16 @@
       </c>
       <c r="O257" s="2" t="inlineStr"/>
       <c r="P257" s="2" t="inlineStr"/>
-      <c r="Q257" s="2" t="inlineStr"/>
-      <c r="R257" s="2" t="inlineStr"/>
+      <c r="Q257" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R257" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="n">
@@ -17123,8 +19171,16 @@
       </c>
       <c r="O258" s="2" t="inlineStr"/>
       <c r="P258" s="2" t="inlineStr"/>
-      <c r="Q258" s="2" t="inlineStr"/>
-      <c r="R258" s="2" t="inlineStr"/>
+      <c r="Q258" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R258" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="n">
@@ -17191,8 +19247,16 @@
       </c>
       <c r="O259" s="2" t="inlineStr"/>
       <c r="P259" s="2" t="inlineStr"/>
-      <c r="Q259" s="2" t="inlineStr"/>
-      <c r="R259" s="2" t="inlineStr"/>
+      <c r="Q259" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R259" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="n">
@@ -17251,8 +19315,16 @@
       <c r="N260" s="2" t="inlineStr"/>
       <c r="O260" s="2" t="inlineStr"/>
       <c r="P260" s="2" t="inlineStr"/>
-      <c r="Q260" s="2" t="inlineStr"/>
-      <c r="R260" s="2" t="inlineStr"/>
+      <c r="Q260" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R260" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="n">
@@ -17311,8 +19383,16 @@
       <c r="N261" s="2" t="inlineStr"/>
       <c r="O261" s="2" t="inlineStr"/>
       <c r="P261" s="2" t="inlineStr"/>
-      <c r="Q261" s="2" t="inlineStr"/>
-      <c r="R261" s="2" t="inlineStr"/>
+      <c r="Q261" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R261" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="n">
@@ -17371,8 +19451,16 @@
       <c r="N262" s="2" t="inlineStr"/>
       <c r="O262" s="2" t="inlineStr"/>
       <c r="P262" s="2" t="inlineStr"/>
-      <c r="Q262" s="2" t="inlineStr"/>
-      <c r="R262" s="2" t="inlineStr"/>
+      <c r="Q262" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R262" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="n">
@@ -17431,8 +19519,16 @@
       <c r="N263" s="2" t="inlineStr"/>
       <c r="O263" s="2" t="inlineStr"/>
       <c r="P263" s="2" t="inlineStr"/>
-      <c r="Q263" s="2" t="inlineStr"/>
-      <c r="R263" s="2" t="inlineStr"/>
+      <c r="Q263" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R263" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="n">
@@ -17499,8 +19595,16 @@
       </c>
       <c r="O264" s="2" t="inlineStr"/>
       <c r="P264" s="2" t="inlineStr"/>
-      <c r="Q264" s="2" t="inlineStr"/>
-      <c r="R264" s="2" t="inlineStr"/>
+      <c r="Q264" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R264" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="n">
@@ -17567,8 +19671,16 @@
       </c>
       <c r="O265" s="2" t="inlineStr"/>
       <c r="P265" s="2" t="inlineStr"/>
-      <c r="Q265" s="2" t="inlineStr"/>
-      <c r="R265" s="2" t="inlineStr"/>
+      <c r="Q265" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R265" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="n">
@@ -17635,8 +19747,16 @@
       </c>
       <c r="O266" s="2" t="inlineStr"/>
       <c r="P266" s="2" t="inlineStr"/>
-      <c r="Q266" s="2" t="inlineStr"/>
-      <c r="R266" s="2" t="inlineStr"/>
+      <c r="Q266" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R266" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="n">
@@ -17699,8 +19819,16 @@
       <c r="N267" s="2" t="inlineStr"/>
       <c r="O267" s="2" t="inlineStr"/>
       <c r="P267" s="2" t="inlineStr"/>
-      <c r="Q267" s="2" t="inlineStr"/>
-      <c r="R267" s="2" t="inlineStr"/>
+      <c r="Q267" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R267" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="n">
@@ -17759,8 +19887,16 @@
       <c r="N268" s="2" t="inlineStr"/>
       <c r="O268" s="2" t="inlineStr"/>
       <c r="P268" s="2" t="inlineStr"/>
-      <c r="Q268" s="2" t="inlineStr"/>
-      <c r="R268" s="2" t="inlineStr"/>
+      <c r="Q268" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R268" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="n">
@@ -17819,8 +19955,16 @@
       <c r="N269" s="2" t="inlineStr"/>
       <c r="O269" s="2" t="inlineStr"/>
       <c r="P269" s="2" t="inlineStr"/>
-      <c r="Q269" s="2" t="inlineStr"/>
-      <c r="R269" s="2" t="inlineStr"/>
+      <c r="Q269" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R269" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="n">
@@ -17879,8 +20023,16 @@
       <c r="N270" s="2" t="inlineStr"/>
       <c r="O270" s="2" t="inlineStr"/>
       <c r="P270" s="2" t="inlineStr"/>
-      <c r="Q270" s="2" t="inlineStr"/>
-      <c r="R270" s="2" t="inlineStr"/>
+      <c r="Q270" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R270" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="n">
@@ -17947,8 +20099,16 @@
       </c>
       <c r="O271" s="2" t="inlineStr"/>
       <c r="P271" s="2" t="inlineStr"/>
-      <c r="Q271" s="2" t="inlineStr"/>
-      <c r="R271" s="2" t="inlineStr"/>
+      <c r="Q271" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R271" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="n">
@@ -18015,8 +20175,16 @@
       </c>
       <c r="O272" s="2" t="inlineStr"/>
       <c r="P272" s="2" t="inlineStr"/>
-      <c r="Q272" s="2" t="inlineStr"/>
-      <c r="R272" s="2" t="inlineStr"/>
+      <c r="Q272" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R272" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="n">
@@ -18075,8 +20243,16 @@
       <c r="N273" s="2" t="inlineStr"/>
       <c r="O273" s="2" t="inlineStr"/>
       <c r="P273" s="2" t="inlineStr"/>
-      <c r="Q273" s="2" t="inlineStr"/>
-      <c r="R273" s="2" t="inlineStr"/>
+      <c r="Q273" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R273" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="n">
@@ -18135,8 +20311,16 @@
       <c r="N274" s="2" t="inlineStr"/>
       <c r="O274" s="2" t="inlineStr"/>
       <c r="P274" s="2" t="inlineStr"/>
-      <c r="Q274" s="2" t="inlineStr"/>
-      <c r="R274" s="2" t="inlineStr"/>
+      <c r="Q274" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R274" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="n">
@@ -18195,8 +20379,16 @@
       <c r="N275" s="2" t="inlineStr"/>
       <c r="O275" s="2" t="inlineStr"/>
       <c r="P275" s="2" t="inlineStr"/>
-      <c r="Q275" s="2" t="inlineStr"/>
-      <c r="R275" s="2" t="inlineStr"/>
+      <c r="Q275" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R275" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="n">
@@ -18255,8 +20447,16 @@
       <c r="N276" s="2" t="inlineStr"/>
       <c r="O276" s="2" t="inlineStr"/>
       <c r="P276" s="2" t="inlineStr"/>
-      <c r="Q276" s="2" t="inlineStr"/>
-      <c r="R276" s="2" t="inlineStr"/>
+      <c r="Q276" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R276" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="n">
@@ -18315,8 +20515,16 @@
       <c r="N277" s="2" t="inlineStr"/>
       <c r="O277" s="2" t="inlineStr"/>
       <c r="P277" s="2" t="inlineStr"/>
-      <c r="Q277" s="2" t="inlineStr"/>
-      <c r="R277" s="2" t="inlineStr"/>
+      <c r="Q277" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R277" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="n">
@@ -18383,8 +20591,16 @@
       </c>
       <c r="O278" s="2" t="inlineStr"/>
       <c r="P278" s="2" t="inlineStr"/>
-      <c r="Q278" s="2" t="inlineStr"/>
-      <c r="R278" s="2" t="inlineStr"/>
+      <c r="Q278" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R278" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="n">
@@ -18451,8 +20667,16 @@
       </c>
       <c r="O279" s="2" t="inlineStr"/>
       <c r="P279" s="2" t="inlineStr"/>
-      <c r="Q279" s="2" t="inlineStr"/>
-      <c r="R279" s="2" t="inlineStr"/>
+      <c r="Q279" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R279" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="n">
@@ -18519,8 +20743,16 @@
       </c>
       <c r="O280" s="2" t="inlineStr"/>
       <c r="P280" s="2" t="inlineStr"/>
-      <c r="Q280" s="2" t="inlineStr"/>
-      <c r="R280" s="2" t="inlineStr"/>
+      <c r="Q280" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R280" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="n">
@@ -18579,8 +20811,16 @@
       <c r="N281" s="2" t="inlineStr"/>
       <c r="O281" s="2" t="inlineStr"/>
       <c r="P281" s="2" t="inlineStr"/>
-      <c r="Q281" s="2" t="inlineStr"/>
-      <c r="R281" s="2" t="inlineStr"/>
+      <c r="Q281" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R281" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="n">
@@ -18647,8 +20887,16 @@
       </c>
       <c r="O282" s="2" t="inlineStr"/>
       <c r="P282" s="2" t="inlineStr"/>
-      <c r="Q282" s="2" t="inlineStr"/>
-      <c r="R282" s="2" t="inlineStr"/>
+      <c r="Q282" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R282" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="n">
@@ -18707,8 +20955,16 @@
       <c r="N283" s="2" t="inlineStr"/>
       <c r="O283" s="2" t="inlineStr"/>
       <c r="P283" s="2" t="inlineStr"/>
-      <c r="Q283" s="2" t="inlineStr"/>
-      <c r="R283" s="2" t="inlineStr"/>
+      <c r="Q283" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R283" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="n">
@@ -18767,8 +21023,16 @@
       <c r="N284" s="2" t="inlineStr"/>
       <c r="O284" s="2" t="inlineStr"/>
       <c r="P284" s="2" t="inlineStr"/>
-      <c r="Q284" s="2" t="inlineStr"/>
-      <c r="R284" s="2" t="inlineStr"/>
+      <c r="Q284" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R284" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="n">
@@ -18827,8 +21091,16 @@
       <c r="N285" s="2" t="inlineStr"/>
       <c r="O285" s="2" t="inlineStr"/>
       <c r="P285" s="2" t="inlineStr"/>
-      <c r="Q285" s="2" t="inlineStr"/>
-      <c r="R285" s="2" t="inlineStr"/>
+      <c r="Q285" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R285" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="n">
@@ -18895,8 +21167,16 @@
       </c>
       <c r="O286" s="2" t="inlineStr"/>
       <c r="P286" s="2" t="inlineStr"/>
-      <c r="Q286" s="2" t="inlineStr"/>
-      <c r="R286" s="2" t="inlineStr"/>
+      <c r="Q286" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R286" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="n">
@@ -18963,8 +21243,16 @@
       </c>
       <c r="O287" s="2" t="inlineStr"/>
       <c r="P287" s="2" t="inlineStr"/>
-      <c r="Q287" s="2" t="inlineStr"/>
-      <c r="R287" s="2" t="inlineStr"/>
+      <c r="Q287" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R287" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="n">
@@ -19023,8 +21311,16 @@
       <c r="N288" s="2" t="inlineStr"/>
       <c r="O288" s="2" t="inlineStr"/>
       <c r="P288" s="2" t="inlineStr"/>
-      <c r="Q288" s="2" t="inlineStr"/>
-      <c r="R288" s="2" t="inlineStr"/>
+      <c r="Q288" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R288" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="n">
@@ -19087,8 +21383,16 @@
       <c r="N289" s="2" t="inlineStr"/>
       <c r="O289" s="2" t="inlineStr"/>
       <c r="P289" s="2" t="inlineStr"/>
-      <c r="Q289" s="2" t="inlineStr"/>
-      <c r="R289" s="2" t="inlineStr"/>
+      <c r="Q289" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R289" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="n">
@@ -19147,8 +21451,16 @@
       <c r="N290" s="2" t="inlineStr"/>
       <c r="O290" s="2" t="inlineStr"/>
       <c r="P290" s="2" t="inlineStr"/>
-      <c r="Q290" s="2" t="inlineStr"/>
-      <c r="R290" s="2" t="inlineStr"/>
+      <c r="Q290" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R290" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="n">
@@ -19215,8 +21527,16 @@
       </c>
       <c r="O291" s="2" t="inlineStr"/>
       <c r="P291" s="2" t="inlineStr"/>
-      <c r="Q291" s="2" t="inlineStr"/>
-      <c r="R291" s="2" t="inlineStr"/>
+      <c r="Q291" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R291" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="n">
@@ -19283,8 +21603,16 @@
       </c>
       <c r="O292" s="2" t="inlineStr"/>
       <c r="P292" s="2" t="inlineStr"/>
-      <c r="Q292" s="2" t="inlineStr"/>
-      <c r="R292" s="2" t="inlineStr"/>
+      <c r="Q292" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R292" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="n">
@@ -19351,8 +21679,16 @@
       </c>
       <c r="O293" s="2" t="inlineStr"/>
       <c r="P293" s="2" t="inlineStr"/>
-      <c r="Q293" s="2" t="inlineStr"/>
-      <c r="R293" s="2" t="inlineStr"/>
+      <c r="Q293" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R293" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="n">
@@ -19411,8 +21747,16 @@
       <c r="N294" s="2" t="inlineStr"/>
       <c r="O294" s="2" t="inlineStr"/>
       <c r="P294" s="2" t="inlineStr"/>
-      <c r="Q294" s="2" t="inlineStr"/>
-      <c r="R294" s="2" t="inlineStr"/>
+      <c r="Q294" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R294" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="n">
@@ -19471,8 +21815,16 @@
       <c r="N295" s="2" t="inlineStr"/>
       <c r="O295" s="2" t="inlineStr"/>
       <c r="P295" s="2" t="inlineStr"/>
-      <c r="Q295" s="2" t="inlineStr"/>
-      <c r="R295" s="2" t="inlineStr"/>
+      <c r="Q295" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R295" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="n">
@@ -19531,8 +21883,16 @@
       <c r="N296" s="2" t="inlineStr"/>
       <c r="O296" s="2" t="inlineStr"/>
       <c r="P296" s="2" t="inlineStr"/>
-      <c r="Q296" s="2" t="inlineStr"/>
-      <c r="R296" s="2" t="inlineStr"/>
+      <c r="Q296" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R296" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="n">
@@ -19595,8 +21955,16 @@
       <c r="N297" s="2" t="inlineStr"/>
       <c r="O297" s="2" t="inlineStr"/>
       <c r="P297" s="2" t="inlineStr"/>
-      <c r="Q297" s="2" t="inlineStr"/>
-      <c r="R297" s="2" t="inlineStr"/>
+      <c r="Q297" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R297" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="n">
@@ -19663,8 +22031,16 @@
       </c>
       <c r="O298" s="2" t="inlineStr"/>
       <c r="P298" s="2" t="inlineStr"/>
-      <c r="Q298" s="2" t="inlineStr"/>
-      <c r="R298" s="2" t="inlineStr"/>
+      <c r="Q298" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R298" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="n">
@@ -19727,8 +22103,16 @@
       </c>
       <c r="O299" s="2" t="inlineStr"/>
       <c r="P299" s="2" t="inlineStr"/>
-      <c r="Q299" s="2" t="inlineStr"/>
-      <c r="R299" s="2" t="inlineStr"/>
+      <c r="Q299" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R299" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="n">
@@ -19795,8 +22179,16 @@
       </c>
       <c r="O300" s="2" t="inlineStr"/>
       <c r="P300" s="2" t="inlineStr"/>
-      <c r="Q300" s="2" t="inlineStr"/>
-      <c r="R300" s="2" t="inlineStr"/>
+      <c r="Q300" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R300" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="n">
@@ -19863,8 +22255,16 @@
       </c>
       <c r="O301" s="2" t="inlineStr"/>
       <c r="P301" s="2" t="inlineStr"/>
-      <c r="Q301" s="2" t="inlineStr"/>
-      <c r="R301" s="2" t="inlineStr"/>
+      <c r="Q301" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R301" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="n">
@@ -19923,8 +22323,16 @@
       <c r="N302" s="2" t="inlineStr"/>
       <c r="O302" s="2" t="inlineStr"/>
       <c r="P302" s="2" t="inlineStr"/>
-      <c r="Q302" s="2" t="inlineStr"/>
-      <c r="R302" s="2" t="inlineStr"/>
+      <c r="Q302" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R302" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="n">
@@ -19983,8 +22391,16 @@
       <c r="N303" s="2" t="inlineStr"/>
       <c r="O303" s="2" t="inlineStr"/>
       <c r="P303" s="2" t="inlineStr"/>
-      <c r="Q303" s="2" t="inlineStr"/>
-      <c r="R303" s="2" t="inlineStr"/>
+      <c r="Q303" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R303" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="n">
@@ -20043,8 +22459,16 @@
       <c r="N304" s="2" t="inlineStr"/>
       <c r="O304" s="2" t="inlineStr"/>
       <c r="P304" s="2" t="inlineStr"/>
-      <c r="Q304" s="2" t="inlineStr"/>
-      <c r="R304" s="2" t="inlineStr"/>
+      <c r="Q304" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R304" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="n">
@@ -20111,8 +22535,16 @@
       </c>
       <c r="O305" s="2" t="inlineStr"/>
       <c r="P305" s="2" t="inlineStr"/>
-      <c r="Q305" s="2" t="inlineStr"/>
-      <c r="R305" s="2" t="inlineStr"/>
+      <c r="Q305" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R305" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="n">
@@ -20175,8 +22607,16 @@
       </c>
       <c r="O306" s="2" t="inlineStr"/>
       <c r="P306" s="2" t="inlineStr"/>
-      <c r="Q306" s="2" t="inlineStr"/>
-      <c r="R306" s="2" t="inlineStr"/>
+      <c r="Q306" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R306" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="n">
@@ -20243,8 +22683,16 @@
       </c>
       <c r="O307" s="2" t="inlineStr"/>
       <c r="P307" s="2" t="inlineStr"/>
-      <c r="Q307" s="2" t="inlineStr"/>
-      <c r="R307" s="2" t="inlineStr"/>
+      <c r="Q307" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R307" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="n">
@@ -20311,8 +22759,16 @@
       </c>
       <c r="O308" s="2" t="inlineStr"/>
       <c r="P308" s="2" t="inlineStr"/>
-      <c r="Q308" s="2" t="inlineStr"/>
-      <c r="R308" s="2" t="inlineStr"/>
+      <c r="Q308" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R308" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="n">
@@ -20375,8 +22831,16 @@
       </c>
       <c r="O309" s="2" t="inlineStr"/>
       <c r="P309" s="2" t="inlineStr"/>
-      <c r="Q309" s="2" t="inlineStr"/>
-      <c r="R309" s="2" t="inlineStr"/>
+      <c r="Q309" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R309" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="n">
@@ -20435,8 +22899,16 @@
       <c r="N310" s="2" t="inlineStr"/>
       <c r="O310" s="2" t="inlineStr"/>
       <c r="P310" s="2" t="inlineStr"/>
-      <c r="Q310" s="2" t="inlineStr"/>
-      <c r="R310" s="2" t="inlineStr"/>
+      <c r="Q310" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R310" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="n">
@@ -20495,8 +22967,16 @@
       <c r="N311" s="2" t="inlineStr"/>
       <c r="O311" s="2" t="inlineStr"/>
       <c r="P311" s="2" t="inlineStr"/>
-      <c r="Q311" s="2" t="inlineStr"/>
-      <c r="R311" s="2" t="inlineStr"/>
+      <c r="Q311" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R311" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="n">
@@ -20563,8 +23043,16 @@
       </c>
       <c r="O312" s="2" t="inlineStr"/>
       <c r="P312" s="2" t="inlineStr"/>
-      <c r="Q312" s="2" t="inlineStr"/>
-      <c r="R312" s="2" t="inlineStr"/>
+      <c r="Q312" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R312" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="n">
@@ -20627,8 +23115,16 @@
       </c>
       <c r="O313" s="2" t="inlineStr"/>
       <c r="P313" s="2" t="inlineStr"/>
-      <c r="Q313" s="2" t="inlineStr"/>
-      <c r="R313" s="2" t="inlineStr"/>
+      <c r="Q313" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R313" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="n">
@@ -20695,8 +23191,16 @@
       </c>
       <c r="O314" s="2" t="inlineStr"/>
       <c r="P314" s="2" t="inlineStr"/>
-      <c r="Q314" s="2" t="inlineStr"/>
-      <c r="R314" s="2" t="inlineStr"/>
+      <c r="Q314" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R314" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="n">
@@ -20755,8 +23259,16 @@
       <c r="N315" s="2" t="inlineStr"/>
       <c r="O315" s="2" t="inlineStr"/>
       <c r="P315" s="2" t="inlineStr"/>
-      <c r="Q315" s="2" t="inlineStr"/>
-      <c r="R315" s="2" t="inlineStr"/>
+      <c r="Q315" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R315" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="n">
@@ -20819,8 +23331,16 @@
       <c r="N316" s="2" t="inlineStr"/>
       <c r="O316" s="2" t="inlineStr"/>
       <c r="P316" s="2" t="inlineStr"/>
-      <c r="Q316" s="2" t="inlineStr"/>
-      <c r="R316" s="2" t="inlineStr"/>
+      <c r="Q316" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R316" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="n">
@@ -20879,8 +23399,16 @@
       <c r="N317" s="2" t="inlineStr"/>
       <c r="O317" s="2" t="inlineStr"/>
       <c r="P317" s="2" t="inlineStr"/>
-      <c r="Q317" s="2" t="inlineStr"/>
-      <c r="R317" s="2" t="inlineStr"/>
+      <c r="Q317" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R317" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="n">
@@ -20939,8 +23467,16 @@
       <c r="N318" s="2" t="inlineStr"/>
       <c r="O318" s="2" t="inlineStr"/>
       <c r="P318" s="2" t="inlineStr"/>
-      <c r="Q318" s="2" t="inlineStr"/>
-      <c r="R318" s="2" t="inlineStr"/>
+      <c r="Q318" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R318" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="n">
@@ -21007,8 +23543,16 @@
       </c>
       <c r="O319" s="2" t="inlineStr"/>
       <c r="P319" s="2" t="inlineStr"/>
-      <c r="Q319" s="2" t="inlineStr"/>
-      <c r="R319" s="2" t="inlineStr"/>
+      <c r="Q319" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R319" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="n">
@@ -21067,8 +23611,16 @@
       <c r="N320" s="2" t="inlineStr"/>
       <c r="O320" s="2" t="inlineStr"/>
       <c r="P320" s="2" t="inlineStr"/>
-      <c r="Q320" s="2" t="inlineStr"/>
-      <c r="R320" s="2" t="inlineStr"/>
+      <c r="Q320" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R320" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="n">
@@ -21135,8 +23687,16 @@
       </c>
       <c r="O321" s="2" t="inlineStr"/>
       <c r="P321" s="2" t="inlineStr"/>
-      <c r="Q321" s="2" t="inlineStr"/>
-      <c r="R321" s="2" t="inlineStr"/>
+      <c r="Q321" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R321" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="n">
@@ -21203,8 +23763,16 @@
       </c>
       <c r="O322" s="2" t="inlineStr"/>
       <c r="P322" s="2" t="inlineStr"/>
-      <c r="Q322" s="2" t="inlineStr"/>
-      <c r="R322" s="2" t="inlineStr"/>
+      <c r="Q322" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R322" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="n">
@@ -21267,8 +23835,16 @@
       <c r="N323" s="2" t="inlineStr"/>
       <c r="O323" s="2" t="inlineStr"/>
       <c r="P323" s="2" t="inlineStr"/>
-      <c r="Q323" s="2" t="inlineStr"/>
-      <c r="R323" s="2" t="inlineStr"/>
+      <c r="Q323" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R323" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="n">
@@ -21327,8 +23903,16 @@
       <c r="N324" s="2" t="inlineStr"/>
       <c r="O324" s="2" t="inlineStr"/>
       <c r="P324" s="2" t="inlineStr"/>
-      <c r="Q324" s="2" t="inlineStr"/>
-      <c r="R324" s="2" t="inlineStr"/>
+      <c r="Q324" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R324" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="n">
@@ -21395,8 +23979,16 @@
       </c>
       <c r="O325" s="2" t="inlineStr"/>
       <c r="P325" s="2" t="inlineStr"/>
-      <c r="Q325" s="2" t="inlineStr"/>
-      <c r="R325" s="2" t="inlineStr"/>
+      <c r="Q325" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R325" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="n">
@@ -21459,8 +24051,16 @@
       <c r="N326" s="2" t="inlineStr"/>
       <c r="O326" s="2" t="inlineStr"/>
       <c r="P326" s="2" t="inlineStr"/>
-      <c r="Q326" s="2" t="inlineStr"/>
-      <c r="R326" s="2" t="inlineStr"/>
+      <c r="Q326" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R326" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="n">
@@ -21519,8 +24119,16 @@
       <c r="N327" s="2" t="inlineStr"/>
       <c r="O327" s="2" t="inlineStr"/>
       <c r="P327" s="2" t="inlineStr"/>
-      <c r="Q327" s="2" t="inlineStr"/>
-      <c r="R327" s="2" t="inlineStr"/>
+      <c r="Q327" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R327" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="n">
@@ -21587,8 +24195,16 @@
       </c>
       <c r="O328" s="2" t="inlineStr"/>
       <c r="P328" s="2" t="inlineStr"/>
-      <c r="Q328" s="2" t="inlineStr"/>
-      <c r="R328" s="2" t="inlineStr"/>
+      <c r="Q328" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R328" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="n">
@@ -21655,8 +24271,16 @@
       </c>
       <c r="O329" s="2" t="inlineStr"/>
       <c r="P329" s="2" t="inlineStr"/>
-      <c r="Q329" s="2" t="inlineStr"/>
-      <c r="R329" s="2" t="inlineStr"/>
+      <c r="Q329" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R329" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="n">
@@ -21715,8 +24339,16 @@
       <c r="N330" s="2" t="inlineStr"/>
       <c r="O330" s="2" t="inlineStr"/>
       <c r="P330" s="2" t="inlineStr"/>
-      <c r="Q330" s="2" t="inlineStr"/>
-      <c r="R330" s="2" t="inlineStr"/>
+      <c r="Q330" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R330" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="n">
@@ -21775,8 +24407,16 @@
       <c r="N331" s="2" t="inlineStr"/>
       <c r="O331" s="2" t="inlineStr"/>
       <c r="P331" s="2" t="inlineStr"/>
-      <c r="Q331" s="2" t="inlineStr"/>
-      <c r="R331" s="2" t="inlineStr"/>
+      <c r="Q331" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R331" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="n">
@@ -21839,8 +24479,16 @@
       <c r="N332" s="2" t="inlineStr"/>
       <c r="O332" s="2" t="inlineStr"/>
       <c r="P332" s="2" t="inlineStr"/>
-      <c r="Q332" s="2" t="inlineStr"/>
-      <c r="R332" s="2" t="inlineStr"/>
+      <c r="Q332" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R332" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="n">
@@ -21903,8 +24551,16 @@
       </c>
       <c r="O333" s="2" t="inlineStr"/>
       <c r="P333" s="2" t="inlineStr"/>
-      <c r="Q333" s="2" t="inlineStr"/>
-      <c r="R333" s="2" t="inlineStr"/>
+      <c r="Q333" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R333" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="n">
@@ -21971,8 +24627,16 @@
       </c>
       <c r="O334" s="2" t="inlineStr"/>
       <c r="P334" s="2" t="inlineStr"/>
-      <c r="Q334" s="2" t="inlineStr"/>
-      <c r="R334" s="2" t="inlineStr"/>
+      <c r="Q334" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R334" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="n">
@@ -22039,8 +24703,16 @@
       </c>
       <c r="O335" s="2" t="inlineStr"/>
       <c r="P335" s="2" t="inlineStr"/>
-      <c r="Q335" s="2" t="inlineStr"/>
-      <c r="R335" s="2" t="inlineStr"/>
+      <c r="Q335" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R335" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="n">
@@ -22107,8 +24779,16 @@
       </c>
       <c r="O336" s="2" t="inlineStr"/>
       <c r="P336" s="2" t="inlineStr"/>
-      <c r="Q336" s="2" t="inlineStr"/>
-      <c r="R336" s="2" t="inlineStr"/>
+      <c r="Q336" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R336" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="n">
@@ -22167,8 +24847,16 @@
       <c r="N337" s="2" t="inlineStr"/>
       <c r="O337" s="2" t="inlineStr"/>
       <c r="P337" s="2" t="inlineStr"/>
-      <c r="Q337" s="2" t="inlineStr"/>
-      <c r="R337" s="2" t="inlineStr"/>
+      <c r="Q337" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R337" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="n">
@@ -22227,8 +24915,16 @@
       <c r="N338" s="2" t="inlineStr"/>
       <c r="O338" s="2" t="inlineStr"/>
       <c r="P338" s="2" t="inlineStr"/>
-      <c r="Q338" s="2" t="inlineStr"/>
-      <c r="R338" s="2" t="inlineStr"/>
+      <c r="Q338" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R338" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="n">
@@ -22287,8 +24983,16 @@
       <c r="N339" s="2" t="inlineStr"/>
       <c r="O339" s="2" t="inlineStr"/>
       <c r="P339" s="2" t="inlineStr"/>
-      <c r="Q339" s="2" t="inlineStr"/>
-      <c r="R339" s="2" t="inlineStr"/>
+      <c r="Q339" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R339" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="n">
@@ -22351,8 +25055,16 @@
       <c r="N340" s="2" t="inlineStr"/>
       <c r="O340" s="2" t="inlineStr"/>
       <c r="P340" s="2" t="inlineStr"/>
-      <c r="Q340" s="2" t="inlineStr"/>
-      <c r="R340" s="2" t="inlineStr"/>
+      <c r="Q340" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R340" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="n">
@@ -22419,8 +25131,16 @@
       </c>
       <c r="O341" s="2" t="inlineStr"/>
       <c r="P341" s="2" t="inlineStr"/>
-      <c r="Q341" s="2" t="inlineStr"/>
-      <c r="R341" s="2" t="inlineStr"/>
+      <c r="Q341" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R341" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="n">
@@ -22487,8 +25207,16 @@
       </c>
       <c r="O342" s="2" t="inlineStr"/>
       <c r="P342" s="2" t="inlineStr"/>
-      <c r="Q342" s="2" t="inlineStr"/>
-      <c r="R342" s="2" t="inlineStr"/>
+      <c r="Q342" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R342" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="n">
@@ -22555,8 +25283,16 @@
       </c>
       <c r="O343" s="2" t="inlineStr"/>
       <c r="P343" s="2" t="inlineStr"/>
-      <c r="Q343" s="2" t="inlineStr"/>
-      <c r="R343" s="2" t="inlineStr"/>
+      <c r="Q343" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R343" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="n">
@@ -22615,8 +25351,16 @@
       <c r="N344" s="2" t="inlineStr"/>
       <c r="O344" s="2" t="inlineStr"/>
       <c r="P344" s="2" t="inlineStr"/>
-      <c r="Q344" s="2" t="inlineStr"/>
-      <c r="R344" s="2" t="inlineStr"/>
+      <c r="Q344" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R344" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="n">
@@ -22679,8 +25423,16 @@
       <c r="N345" s="2" t="inlineStr"/>
       <c r="O345" s="2" t="inlineStr"/>
       <c r="P345" s="2" t="inlineStr"/>
-      <c r="Q345" s="2" t="inlineStr"/>
-      <c r="R345" s="2" t="inlineStr"/>
+      <c r="Q345" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R345" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="n">
@@ -22739,8 +25491,16 @@
       <c r="N346" s="2" t="inlineStr"/>
       <c r="O346" s="2" t="inlineStr"/>
       <c r="P346" s="2" t="inlineStr"/>
-      <c r="Q346" s="2" t="inlineStr"/>
-      <c r="R346" s="2" t="inlineStr"/>
+      <c r="Q346" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R346" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="2" t="n">
@@ -22803,8 +25563,16 @@
       <c r="N347" s="2" t="inlineStr"/>
       <c r="O347" s="2" t="inlineStr"/>
       <c r="P347" s="2" t="inlineStr"/>
-      <c r="Q347" s="2" t="inlineStr"/>
-      <c r="R347" s="2" t="inlineStr"/>
+      <c r="Q347" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R347" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="n">
@@ -22867,8 +25635,16 @@
       <c r="N348" s="2" t="inlineStr"/>
       <c r="O348" s="2" t="inlineStr"/>
       <c r="P348" s="2" t="inlineStr"/>
-      <c r="Q348" s="2" t="inlineStr"/>
-      <c r="R348" s="2" t="inlineStr"/>
+      <c r="Q348" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R348" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="2" t="n">
@@ -22935,8 +25711,16 @@
       </c>
       <c r="O349" s="2" t="inlineStr"/>
       <c r="P349" s="2" t="inlineStr"/>
-      <c r="Q349" s="2" t="inlineStr"/>
-      <c r="R349" s="2" t="inlineStr"/>
+      <c r="Q349" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R349" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="n">
@@ -23003,8 +25787,16 @@
       </c>
       <c r="O350" s="2" t="inlineStr"/>
       <c r="P350" s="2" t="inlineStr"/>
-      <c r="Q350" s="2" t="inlineStr"/>
-      <c r="R350" s="2" t="inlineStr"/>
+      <c r="Q350" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R350" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="n">
@@ -23063,8 +25855,16 @@
       <c r="N351" s="2" t="inlineStr"/>
       <c r="O351" s="2" t="inlineStr"/>
       <c r="P351" s="2" t="inlineStr"/>
-      <c r="Q351" s="2" t="inlineStr"/>
-      <c r="R351" s="2" t="inlineStr"/>
+      <c r="Q351" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R351" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="n">
@@ -23123,8 +25923,16 @@
       <c r="N352" s="2" t="inlineStr"/>
       <c r="O352" s="2" t="inlineStr"/>
       <c r="P352" s="2" t="inlineStr"/>
-      <c r="Q352" s="2" t="inlineStr"/>
-      <c r="R352" s="2" t="inlineStr"/>
+      <c r="Q352" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R352" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="n">
@@ -23183,8 +25991,16 @@
       <c r="N353" s="2" t="inlineStr"/>
       <c r="O353" s="2" t="inlineStr"/>
       <c r="P353" s="2" t="inlineStr"/>
-      <c r="Q353" s="2" t="inlineStr"/>
-      <c r="R353" s="2" t="inlineStr"/>
+      <c r="Q353" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R353" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="n">
@@ -23243,8 +26059,16 @@
       <c r="N354" s="2" t="inlineStr"/>
       <c r="O354" s="2" t="inlineStr"/>
       <c r="P354" s="2" t="inlineStr"/>
-      <c r="Q354" s="2" t="inlineStr"/>
-      <c r="R354" s="2" t="inlineStr"/>
+      <c r="Q354" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R354" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="n">
@@ -23303,8 +26127,16 @@
       <c r="N355" s="2" t="inlineStr"/>
       <c r="O355" s="2" t="inlineStr"/>
       <c r="P355" s="2" t="inlineStr"/>
-      <c r="Q355" s="2" t="inlineStr"/>
-      <c r="R355" s="2" t="inlineStr"/>
+      <c r="Q355" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R355" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="n">
@@ -23371,8 +26203,16 @@
       </c>
       <c r="O356" s="2" t="inlineStr"/>
       <c r="P356" s="2" t="inlineStr"/>
-      <c r="Q356" s="2" t="inlineStr"/>
-      <c r="R356" s="2" t="inlineStr"/>
+      <c r="Q356" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R356" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="2" t="n">
@@ -23439,8 +26279,16 @@
       </c>
       <c r="O357" s="2" t="inlineStr"/>
       <c r="P357" s="2" t="inlineStr"/>
-      <c r="Q357" s="2" t="inlineStr"/>
-      <c r="R357" s="2" t="inlineStr"/>
+      <c r="Q357" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R357" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="n">
@@ -23499,8 +26347,16 @@
       <c r="N358" s="2" t="inlineStr"/>
       <c r="O358" s="2" t="inlineStr"/>
       <c r="P358" s="2" t="inlineStr"/>
-      <c r="Q358" s="2" t="inlineStr"/>
-      <c r="R358" s="2" t="inlineStr"/>
+      <c r="Q358" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R358" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="n">
@@ -23567,8 +26423,16 @@
       </c>
       <c r="O359" s="2" t="inlineStr"/>
       <c r="P359" s="2" t="inlineStr"/>
-      <c r="Q359" s="2" t="inlineStr"/>
-      <c r="R359" s="2" t="inlineStr"/>
+      <c r="Q359" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R359" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="n">
@@ -23627,8 +26491,16 @@
       <c r="N360" s="2" t="inlineStr"/>
       <c r="O360" s="2" t="inlineStr"/>
       <c r="P360" s="2" t="inlineStr"/>
-      <c r="Q360" s="2" t="inlineStr"/>
-      <c r="R360" s="2" t="inlineStr"/>
+      <c r="Q360" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R360" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="n">
@@ -23687,8 +26559,16 @@
       <c r="N361" s="2" t="inlineStr"/>
       <c r="O361" s="2" t="inlineStr"/>
       <c r="P361" s="2" t="inlineStr"/>
-      <c r="Q361" s="2" t="inlineStr"/>
-      <c r="R361" s="2" t="inlineStr"/>
+      <c r="Q361" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R361" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="n">
@@ -23759,8 +26639,16 @@
       </c>
       <c r="O362" s="2" t="inlineStr"/>
       <c r="P362" s="2" t="inlineStr"/>
-      <c r="Q362" s="2" t="inlineStr"/>
-      <c r="R362" s="2" t="inlineStr"/>
+      <c r="Q362" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R362" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="n">
@@ -23827,8 +26715,16 @@
       </c>
       <c r="O363" s="2" t="inlineStr"/>
       <c r="P363" s="2" t="inlineStr"/>
-      <c r="Q363" s="2" t="inlineStr"/>
-      <c r="R363" s="2" t="inlineStr"/>
+      <c r="Q363" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R363" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="n">
@@ -23895,8 +26791,16 @@
       </c>
       <c r="O364" s="2" t="inlineStr"/>
       <c r="P364" s="2" t="inlineStr"/>
-      <c r="Q364" s="2" t="inlineStr"/>
-      <c r="R364" s="2" t="inlineStr"/>
+      <c r="Q364" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R364" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="n">
@@ -23955,8 +26859,16 @@
       <c r="N365" s="2" t="inlineStr"/>
       <c r="O365" s="2" t="inlineStr"/>
       <c r="P365" s="2" t="inlineStr"/>
-      <c r="Q365" s="2" t="inlineStr"/>
-      <c r="R365" s="2" t="inlineStr"/>
+      <c r="Q365" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R365" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="n">
@@ -24023,8 +26935,16 @@
       </c>
       <c r="O366" s="2" t="inlineStr"/>
       <c r="P366" s="2" t="inlineStr"/>
-      <c r="Q366" s="2" t="inlineStr"/>
-      <c r="R366" s="2" t="inlineStr"/>
+      <c r="Q366" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R366" s="2" t="inlineStr">
+        <is>
+          <t>Approved by Owen, 18 Oct 2026 (whole pipeline as proposed)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:R366"/>
